--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Pagina Web de Riesgo VS\Horario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155C489B-A603-49D9-81E7-222D9BA7A249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="26">
   <si>
     <t>GESTOR</t>
   </si>
@@ -658,16 +658,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O77"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -714,7 +714,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -759,7 +759,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -806,7 +806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -853,7 +853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -900,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -947,7 +947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -994,7 +994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
@@ -1589,7 +1589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>0</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>0</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
@@ -2209,7 +2209,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2469,8 +2469,319 @@
         <v>19</v>
       </c>
     </row>
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46167</v>
+      </c>
+      <c r="C66" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D66" s="1">
+        <v>46169</v>
+      </c>
+      <c r="E66" s="1">
+        <v>46170</v>
+      </c>
+      <c r="F66" s="1">
+        <v>46171</v>
+      </c>
+      <c r="G66" s="1">
+        <v>46172</v>
+      </c>
+      <c r="H66" s="1">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="13"/>
+      <c r="B67" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A66:A67"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A27:A28"/>
@@ -2483,17 +2794,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -2694,6 +2994,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2704,17 +3015,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2733,6 +3033,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Pagina Web de Riesgo VS\Horario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E724598E-DA6A-46A9-9494-576E9250E565}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="26">
   <si>
     <t>GESTOR</t>
   </si>
@@ -186,7 +186,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,8 +235,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -285,12 +291,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -314,14 +346,20 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -658,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -668,7 +706,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -715,7 +753,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
+      <c r="A2" s="13"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1230,7 +1268,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1256,7 +1294,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
+      <c r="A15" s="13"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1540,7 +1578,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1566,7 +1604,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
+      <c r="A28" s="13"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1850,7 +1888,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -1876,7 +1914,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
+      <c r="A41" s="11"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2160,7 +2198,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2186,7 +2224,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="13"/>
+      <c r="A54" s="11"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2470,7 +2508,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2496,7 +2534,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
+      <c r="A67" s="11"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2779,8 +2817,316 @@
         <v>10</v>
       </c>
     </row>
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46175</v>
+      </c>
+      <c r="D79" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E79" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F79" s="1">
+        <v>46178</v>
+      </c>
+      <c r="G79" s="1">
+        <v>46179</v>
+      </c>
+      <c r="H79" s="1">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="11"/>
+      <c r="B80" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G84" s="14"/>
+      <c r="H84" s="15"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
@@ -2794,6 +3140,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -2994,27 +3360,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3031,23 +3396,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E724598E-DA6A-46A9-9494-576E9250E565}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705138F6-F38D-4977-96B2-2ADFBE7B6659}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -349,17 +349,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -697,16 +697,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
   <dimension ref="A1:O90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -752,8 +752,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -797,7 +797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -844,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -891,7 +891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -985,7 +985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1267,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1293,8 +1293,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="15"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1577,8 +1577,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1603,8 +1603,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>0</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
         <v>0</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="11"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
@@ -2247,7 +2247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
         <v>0</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="11"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -2557,7 +2557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>0</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="11"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
@@ -2867,7 +2867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -2935,8 +2935,8 @@
       <c r="E83" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>9</v>
+      <c r="F83" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>10</v>
@@ -2945,7 +2945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -2964,10 +2964,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="14"/>
-      <c r="H84" s="15"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G84" s="12"/>
+      <c r="H84" s="13"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3140,15 +3140,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
@@ -3157,6 +3148,15 @@
     <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3361,20 +3361,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
     <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705138F6-F38D-4977-96B2-2ADFBE7B6659}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAD4FFD9-4F4D-41E9-894C-DCFE18A56FA3}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="26">
   <si>
     <t>GESTOR</t>
   </si>
@@ -696,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
@@ -3123,8 +3123,293 @@
         <v>10</v>
       </c>
     </row>
+    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C92" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D92" s="1">
+        <v>46183</v>
+      </c>
+      <c r="E92" s="1">
+        <v>46184</v>
+      </c>
+      <c r="F92" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G92" s="1">
+        <v>46186</v>
+      </c>
+      <c r="H92" s="1">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="11"/>
+      <c r="B93" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A92:A93"/>
     <mergeCell ref="A79:A80"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
@@ -3140,26 +3425,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -3360,26 +3625,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3396,4 +3662,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAD4FFD9-4F4D-41E9-894C-DCFE18A56FA3}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDBDBEEF-DC36-48C1-B3C7-7D4C7FB3AC40}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="26">
   <si>
     <t>GESTOR</t>
   </si>
@@ -696,16 +696,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O114"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -752,7 +752,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -844,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -891,7 +891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -985,7 +985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>0</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
@@ -1627,7 +1627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>0</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>0</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
@@ -2247,7 +2247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>0</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -2557,7 +2557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>0</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="11"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
@@ -2867,7 +2867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -2967,7 +2967,7 @@
       <c r="G84" s="12"/>
       <c r="H84" s="13"/>
     </row>
-    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>0</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="11"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
@@ -3173,7 +3173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3407,8 +3407,293 @@
         <v>10</v>
       </c>
     </row>
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C104" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D104" s="1">
+        <v>46190</v>
+      </c>
+      <c r="E104" s="1">
+        <v>46191</v>
+      </c>
+      <c r="F104" s="1">
+        <v>46192</v>
+      </c>
+      <c r="G104" s="1">
+        <v>46193</v>
+      </c>
+      <c r="H104" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="11"/>
+      <c r="B105" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="A104:A105"/>
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="A79:A80"/>
     <mergeCell ref="G84:H84"/>
@@ -3425,6 +3710,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -3625,27 +3930,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3662,23 +3966,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDBDBEEF-DC36-48C1-B3C7-7D4C7FB3AC40}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DDFBCE9-CE24-42BA-8B47-C29FBD3CB23A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="26">
   <si>
     <t>GESTOR</t>
   </si>
@@ -349,17 +349,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -696,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -706,7 +706,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -753,7 +753,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
+      <c r="A2" s="13"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1268,7 +1268,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1294,7 +1294,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="13"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1604,7 +1604,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+      <c r="A28" s="13"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2964,8 +2964,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="12"/>
-      <c r="H84" s="13"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="15"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
@@ -3691,18 +3691,303 @@
         <v>10</v>
       </c>
     </row>
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D116" s="1">
+        <v>46197</v>
+      </c>
+      <c r="E116" s="1">
+        <v>46198</v>
+      </c>
+      <c r="F116" s="1">
+        <v>46199</v>
+      </c>
+      <c r="G116" s="1">
+        <v>46200</v>
+      </c>
+      <c r="H116" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="11"/>
+      <c r="B117" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H119" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
+  <mergeCells count="11">
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3710,26 +3995,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -3930,26 +4195,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3966,4 +4232,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DDFBCE9-CE24-42BA-8B47-C29FBD3CB23A}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{052E6E8A-249E-4FB9-A97F-4A15CCC6428E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="28680" yWindow="5280" windowWidth="23280" windowHeight="12480" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="30">
   <si>
     <t>GESTOR</t>
   </si>
@@ -117,6 +117,18 @@
   </si>
   <si>
     <t>Dia de la Familia</t>
+  </si>
+  <si>
+    <t>11am - 6pm</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Luis</t>
   </si>
 </sst>
 </file>
@@ -322,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -349,17 +361,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -696,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -706,7 +721,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -753,7 +768,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
+      <c r="A2" s="16"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1268,7 +1283,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1294,7 +1309,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1578,7 +1593,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1604,7 +1619,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1888,7 +1903,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -1914,7 +1929,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="11"/>
+      <c r="A41" s="14"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2198,7 +2213,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2224,7 +2239,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="11"/>
+      <c r="A54" s="14"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2508,7 +2523,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2534,7 +2549,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="11"/>
+      <c r="A67" s="14"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2818,7 +2833,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -2844,7 +2859,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="11"/>
+      <c r="A80" s="14"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -2964,8 +2979,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="14"/>
-      <c r="H84" s="15"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="13"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
@@ -3124,7 +3139,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3150,7 +3165,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="11"/>
+      <c r="A93" s="14"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3408,7 +3423,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
+      <c r="A104" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3434,7 +3449,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="11"/>
+      <c r="A105" s="14"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3692,7 +3707,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="11" t="s">
+      <c r="A116" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3718,7 +3733,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="11"/>
+      <c r="A117" s="14"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -3813,7 +3828,7 @@
         <v>9</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H120" s="5" t="s">
         <v>10</v>
@@ -3868,7 +3883,7 @@
         <v>10</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3972,6 +3987,420 @@
         <v>13</v>
       </c>
       <c r="H126" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H127" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A130" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46202</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D130" s="1">
+        <v>46204</v>
+      </c>
+      <c r="E130" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F130" s="1">
+        <v>46206</v>
+      </c>
+      <c r="G130" s="1">
+        <v>46207</v>
+      </c>
+      <c r="H130" s="1">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A131" s="11"/>
+      <c r="B131" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H133" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H134" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H143" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3995,6 +4424,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -4195,27 +4644,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4232,23 +4680,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{052E6E8A-249E-4FB9-A97F-4A15CCC6428E}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEBE6699-5698-4B61-85A0-119C70C71826}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="5280" windowWidth="23280" windowHeight="12480" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="30">
   <si>
     <t>GESTOR</t>
   </si>
@@ -711,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O158"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -4404,8 +4404,371 @@
         <v>10</v>
       </c>
     </row>
+    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C145" s="1">
+        <v>46210</v>
+      </c>
+      <c r="D145" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E145" s="1">
+        <v>46212</v>
+      </c>
+      <c r="F145" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G145" s="1">
+        <v>46214</v>
+      </c>
+      <c r="H145" s="1">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A146" s="14"/>
+      <c r="B146" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A145:A146"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="A116:A117"/>
@@ -4424,15 +4787,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
@@ -4441,6 +4795,15 @@
     <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4645,20 +5008,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
     <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEBE6699-5698-4B61-85A0-119C70C71826}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B53325D-D905-448C-B9BF-A4927D1D823E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="30">
   <si>
     <t>GESTOR</t>
   </si>
@@ -361,14 +361,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -711,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O158"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -1903,7 +1903,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -1929,7 +1929,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
+      <c r="A41" s="12"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2213,7 +2213,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2239,7 +2239,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="14"/>
+      <c r="A54" s="12"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2523,7 +2523,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2549,7 +2549,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="14"/>
+      <c r="A67" s="12"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2833,7 +2833,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="14"/>
+      <c r="A80" s="12"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -2979,8 +2979,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="12"/>
-      <c r="H84" s="13"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="14"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
@@ -3139,7 +3139,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3165,7 +3165,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="14"/>
+      <c r="A93" s="12"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3423,7 +3423,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="14" t="s">
+      <c r="A104" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3449,7 +3449,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="14"/>
+      <c r="A105" s="12"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3707,7 +3707,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="14" t="s">
+      <c r="A116" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3733,7 +3733,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="14"/>
+      <c r="A117" s="12"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4405,7 +4405,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="14" t="s">
+      <c r="A145" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4431,7 +4431,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="14"/>
+      <c r="A146" s="12"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4766,8 +4766,371 @@
         <v>11</v>
       </c>
     </row>
+    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" s="1">
+        <v>46216</v>
+      </c>
+      <c r="C160" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46218</v>
+      </c>
+      <c r="E160" s="1">
+        <v>46219</v>
+      </c>
+      <c r="F160" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G160" s="1">
+        <v>46221</v>
+      </c>
+      <c r="H160" s="1">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="12"/>
+      <c r="B161" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
@@ -4787,26 +5150,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -5007,26 +5350,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5043,4 +5387,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B53325D-D905-448C-B9BF-A4927D1D823E}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AA4026B-ECF4-42D8-9DFD-53DCFCBA9E3E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="35">
   <si>
     <t>GESTOR</t>
   </si>
@@ -130,6 +130,21 @@
   <si>
     <t>Luis</t>
   </si>
+  <si>
+    <t>8am - 2pm</t>
+  </si>
+  <si>
+    <t>8am - 5pm</t>
+  </si>
+  <si>
+    <t>2pm - 8pm</t>
+  </si>
+  <si>
+    <t>2pm - 11pm</t>
+  </si>
+  <si>
+    <t>Disponible</t>
+  </si>
 </sst>
 </file>
 
@@ -198,7 +213,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,6 +266,12 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -334,7 +355,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -376,6 +397,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="20% - Énfasis4" xfId="1" builtinId="42"/>
@@ -711,16 +733,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O173"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O188"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -767,7 +789,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -812,7 +834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -859,7 +881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -906,7 +928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -953,7 +975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1000,7 +1022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1047,7 +1069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1094,7 +1116,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1141,7 +1163,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1188,7 +1210,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1235,7 +1257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1282,7 +1304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>0</v>
       </c>
@@ -1308,7 +1330,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="16"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1332,7 +1354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1358,7 +1380,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1384,7 +1406,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1410,7 +1432,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1436,7 +1458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1462,7 +1484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1488,7 +1510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1514,7 +1536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1540,7 +1562,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1566,7 +1588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1592,7 +1614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>0</v>
       </c>
@@ -1618,7 +1640,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
@@ -1642,7 +1664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1668,7 +1690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1694,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1720,7 +1742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1746,7 +1768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1772,7 +1794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1798,7 +1820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1824,7 +1846,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1850,7 +1872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -1876,7 +1898,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -1902,7 +1924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>0</v>
       </c>
@@ -1928,7 +1950,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
@@ -1952,7 +1974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -1978,7 +2000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2004,7 +2026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2030,7 +2052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2056,7 +2078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2082,7 +2104,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2108,7 +2130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2134,7 +2156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2160,7 +2182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2186,7 +2208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2212,7 +2234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>0</v>
       </c>
@@ -2238,7 +2260,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="12"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
@@ -2262,7 +2284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2288,7 +2310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2314,7 +2336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2340,7 +2362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2366,7 +2388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2392,7 +2414,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2418,7 +2440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2444,7 +2466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2470,7 +2492,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2496,7 +2518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2522,7 +2544,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>0</v>
       </c>
@@ -2548,7 +2570,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="12"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -2572,7 +2594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2598,7 +2620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2624,7 +2646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2650,7 +2672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2676,7 +2698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2702,7 +2724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -2728,7 +2750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2754,7 +2776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -2780,7 +2802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -2806,7 +2828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -2832,7 +2854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>0</v>
       </c>
@@ -2858,7 +2880,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="12"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
@@ -2882,7 +2904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -2908,7 +2930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -2934,7 +2956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -2960,7 +2982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -2982,7 +3004,7 @@
       <c r="G84" s="13"/>
       <c r="H84" s="14"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3008,7 +3030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3034,7 +3056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3060,7 +3082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3086,7 +3108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3112,7 +3134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3138,7 +3160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
         <v>0</v>
       </c>
@@ -3164,7 +3186,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="12"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
@@ -3188,7 +3210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3214,7 +3236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3240,7 +3262,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3266,7 +3288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3292,7 +3314,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3318,7 +3340,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3344,7 +3366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3370,7 +3392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3396,7 +3418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3422,7 +3444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
         <v>0</v>
       </c>
@@ -3448,7 +3470,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="12"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
@@ -3472,7 +3494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3498,7 +3520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3524,7 +3546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3550,7 +3572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3576,7 +3598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3602,7 +3624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3628,7 +3650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3654,7 +3676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -3680,7 +3702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -3706,7 +3728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
         <v>0</v>
       </c>
@@ -3732,7 +3754,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="12"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
@@ -3756,7 +3778,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -3782,7 +3804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -3808,7 +3830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -3834,7 +3856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -3860,7 +3882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -3886,7 +3908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -3912,7 +3934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -3938,7 +3960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -3964,7 +3986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -3990,7 +4012,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4016,7 +4038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4042,7 +4064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4068,7 +4090,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4092,7 +4114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4118,7 +4140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4144,7 +4166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4170,7 +4192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4196,7 +4218,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4222,7 +4244,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4248,7 +4270,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4274,7 +4296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4300,7 +4322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4326,7 +4348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4352,7 +4374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4378,7 +4400,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4404,7 +4426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
         <v>0</v>
       </c>
@@ -4430,7 +4452,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="12"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
@@ -4454,7 +4476,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4480,7 +4502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4506,7 +4528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4532,7 +4554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4558,7 +4580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4584,7 +4606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4610,7 +4632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4636,7 +4658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4662,7 +4684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -4688,7 +4710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -4714,7 +4736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -4740,7 +4762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -4766,7 +4788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
         <v>0</v>
       </c>
@@ -4792,7 +4814,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
@@ -4816,7 +4838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -4842,7 +4864,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -4868,7 +4890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -4894,7 +4916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -4920,7 +4942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -4946,7 +4968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -4972,7 +4994,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -4998,7 +5020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5024,7 +5046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5050,7 +5072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5076,7 +5098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5102,7 +5124,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5128,18 +5150,381 @@
         <v>10</v>
       </c>
     </row>
+    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A175" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B175" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C175" s="1">
+        <v>46224</v>
+      </c>
+      <c r="D175" s="1">
+        <v>46225</v>
+      </c>
+      <c r="E175" s="1">
+        <v>46226</v>
+      </c>
+      <c r="F175" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G175" s="1">
+        <v>46228</v>
+      </c>
+      <c r="H175" s="1">
+        <v>46229</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A176" s="12"/>
+      <c r="B176" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G179" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H184" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B187" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H187" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B188" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G188" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H188" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A104:A105"/>
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="A79:A80"/>
@@ -5150,6 +5535,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -5350,15 +5744,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5371,6 +5756,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5389,14 +5782,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{9D16BB9E-340D-4BDB-B5ED-422BF14398D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AA4026B-ECF4-42D8-9DFD-53DCFCBA9E3E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{F0C57C6A-092A-43C3-B98A-364FA8EFBE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="36">
   <si>
     <t>GESTOR</t>
   </si>
@@ -145,12 +145,15 @@
   <si>
     <t>Disponible</t>
   </si>
+  <si>
+    <t>Dia de Votación</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,8 +215,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,6 +297,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -355,7 +387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -382,7 +414,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -391,13 +430,23 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="20% - Énfasis4" xfId="1" builtinId="42"/>
@@ -414,6 +463,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -733,17 +786,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O188"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O203"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -789,8 +843,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -834,7 +888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -881,7 +935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -928,7 +982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -975,7 +1029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1022,7 +1076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1069,7 +1123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1116,7 +1170,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1163,7 +1217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1210,7 +1264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1257,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1304,8 +1358,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1330,8 +1384,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1354,7 +1408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1380,7 +1434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1406,7 +1460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1432,7 +1486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1458,7 +1512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1484,7 +1538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1510,7 +1564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1536,7 +1590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1562,7 +1616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1588,7 +1642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1614,8 +1668,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1640,8 +1694,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1664,7 +1718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1690,7 +1744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1716,7 +1770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1742,7 +1796,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1768,7 +1822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1794,7 +1848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1820,7 +1874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1846,7 +1900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1872,7 +1926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -1898,7 +1952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -1924,8 +1978,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -1950,8 +2004,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -1974,7 +2028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2000,7 +2054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2026,7 +2080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2052,7 +2106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2078,7 +2132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2104,7 +2158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2130,7 +2184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2156,7 +2210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2182,7 +2236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2208,7 +2262,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2234,8 +2288,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="12" t="s">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2260,8 +2314,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="12"/>
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="13"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2284,7 +2338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2310,7 +2364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2336,7 +2390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2362,7 +2416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2388,7 +2442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2414,7 +2468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2440,7 +2494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2466,7 +2520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2492,7 +2546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2518,7 +2572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2544,8 +2598,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="12" t="s">
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2570,8 +2624,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="13"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2594,7 +2648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2620,7 +2674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2646,7 +2700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2672,7 +2726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2698,7 +2752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2724,7 +2778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -2750,7 +2804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2776,7 +2830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -2802,7 +2856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -2828,7 +2882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -2854,8 +2908,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="12" t="s">
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -2880,8 +2934,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="12"/>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="13"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -2904,7 +2958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -2930,7 +2984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -2956,7 +3010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -2982,7 +3036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3001,10 +3055,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="13"/>
-      <c r="H84" s="14"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G84" s="16"/>
+      <c r="H84" s="17"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3030,7 +3084,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3056,7 +3110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3082,7 +3136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3108,7 +3162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3134,7 +3188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3160,8 +3214,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="12" t="s">
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3186,8 +3240,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="12"/>
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="13"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3210,7 +3264,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3236,7 +3290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3262,7 +3316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3288,7 +3342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3314,7 +3368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3340,7 +3394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3366,7 +3420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3392,7 +3446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3418,7 +3472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3444,8 +3498,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="12" t="s">
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3470,8 +3524,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="12"/>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="13"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3494,7 +3548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3520,7 +3574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3546,7 +3600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3572,7 +3626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3598,7 +3652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3624,7 +3678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3650,7 +3704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3676,7 +3730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -3702,7 +3756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -3728,8 +3782,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="12" t="s">
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3754,8 +3808,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="12"/>
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="13"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -3778,7 +3832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -3804,7 +3858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -3830,7 +3884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -3856,7 +3910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -3882,7 +3936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -3908,7 +3962,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -3934,7 +3988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -3960,7 +4014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -3986,7 +4040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4012,7 +4066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4038,7 +4092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4064,7 +4118,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4090,7 +4144,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4114,7 +4168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4140,7 +4194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4166,7 +4220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4192,7 +4246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4218,7 +4272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4244,7 +4298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4270,7 +4324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4296,7 +4350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4322,7 +4376,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4348,7 +4402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4374,7 +4428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4400,7 +4454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4426,8 +4480,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="12" t="s">
+    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4452,8 +4506,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="12"/>
+    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A146" s="13"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4476,7 +4530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4502,7 +4556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4528,7 +4582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4554,7 +4608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4580,7 +4634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4606,7 +4660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4632,7 +4686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4658,7 +4712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4684,7 +4738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -4710,7 +4764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -4736,7 +4790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -4762,7 +4816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -4788,8 +4842,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="12" t="s">
+    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -4814,8 +4868,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="12"/>
+    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="13"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -4838,7 +4892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -4864,7 +4918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -4890,7 +4944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -4916,7 +4970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -4942,7 +4996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -4968,7 +5022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -4994,7 +5048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5020,7 +5074,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5046,7 +5100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5072,7 +5126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5098,7 +5152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5124,7 +5178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5150,8 +5204,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="12" t="s">
+    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5176,8 +5230,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="12"/>
+    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="13"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5200,7 +5254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5226,7 +5280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5252,7 +5306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5278,7 +5332,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5304,7 +5358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5330,7 +5384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5356,7 +5410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5382,7 +5436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5408,7 +5462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5434,7 +5488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5460,11 +5514,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B187" s="17" t="s">
+      <c r="B187" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -5486,11 +5540,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B188" s="17" t="s">
+      <c r="B188" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -5505,15 +5559,384 @@
       <c r="F188" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G188" s="17" t="s">
+      <c r="G188" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H188" s="17" t="s">
+      <c r="H188" s="12" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A190" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B190" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C190" s="1">
+        <v>46231</v>
+      </c>
+      <c r="D190" s="1">
+        <v>46232</v>
+      </c>
+      <c r="E190" s="1">
+        <v>46233</v>
+      </c>
+      <c r="F190" s="1">
+        <v>46234</v>
+      </c>
+      <c r="G190" s="1">
+        <v>46235</v>
+      </c>
+      <c r="H190" s="1">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A191" s="13"/>
+      <c r="B191" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B192" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D192" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G192" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H192" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A193" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G193" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H193" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A194" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G194" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A195" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G195" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H195" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A196" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B196" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G196" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H196" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A197" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G197" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H197" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A198" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B198" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D198" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F198" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A199" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F199" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G199" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H199" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A200" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G200" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H200" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H201" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A202" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G202" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H202" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B203" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C203" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D203" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E203" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F203" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G203" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="H203" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
@@ -5522,12 +5945,6 @@
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5535,15 +5952,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -5744,6 +6152,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5756,14 +6173,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5782,6 +6191,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{F0C57C6A-092A-43C3-B98A-364FA8EFBE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -219,24 +219,28 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -415,21 +419,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,6 +436,21 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="20% - Énfasis4" xfId="1" builtinId="42"/>
@@ -465,8 +469,57 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D4ADAC6-934E-F14F-7EBC-3B184D690824}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6080760" y="38221920"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -787,17 +840,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
   <dimension ref="A1:O203"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -843,8 +896,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="26"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -888,7 +941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -935,7 +988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -982,7 +1035,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1029,7 +1082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1076,7 +1129,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1123,7 +1176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1170,7 +1223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1217,7 +1270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1264,7 +1317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1311,7 +1364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1358,8 +1411,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1384,8 +1437,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="26"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1408,7 +1461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1434,7 +1487,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1460,7 +1513,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1486,7 +1539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1512,7 +1565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1538,7 +1591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1564,7 +1617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1590,7 +1643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1616,7 +1669,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1642,7 +1695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1668,8 +1721,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1694,8 +1747,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="26"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1718,7 +1771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1744,7 +1797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1770,7 +1823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1796,7 +1849,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1822,7 +1875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1848,7 +1901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1874,7 +1927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1900,7 +1953,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1926,7 +1979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -1952,7 +2005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -1978,8 +2031,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2004,8 +2057,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="22"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2028,7 +2081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2054,7 +2107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2080,7 +2133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2106,7 +2159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2132,7 +2185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2158,7 +2211,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2184,7 +2237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2210,7 +2263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2236,7 +2289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2262,7 +2315,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2288,8 +2341,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
+    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2314,8 +2367,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="13"/>
+    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="22"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2338,7 +2391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2364,7 +2417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2390,7 +2443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2416,7 +2469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2442,7 +2495,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2468,7 +2521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2494,7 +2547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2520,7 +2573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2546,7 +2599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2572,7 +2625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2598,8 +2651,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
+    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2624,8 +2677,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
+    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="22"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2648,7 +2701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2674,7 +2727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2700,7 +2753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2726,7 +2779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2752,7 +2805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2778,7 +2831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -2804,7 +2857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2830,7 +2883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -2856,7 +2909,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -2882,7 +2935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -2908,8 +2961,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
+    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -2934,8 +2987,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="22"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -2958,7 +3011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -2984,7 +3037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3010,7 +3063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3036,7 +3089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3055,10 +3108,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="16"/>
-      <c r="H84" s="17"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G84" s="23"/>
+      <c r="H84" s="24"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3084,7 +3137,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3110,7 +3163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3136,7 +3189,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3162,7 +3215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3188,7 +3241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3214,8 +3267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="13" t="s">
+    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3240,8 +3293,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
+    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="22"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3264,7 +3317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3290,7 +3343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3316,7 +3369,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3342,7 +3395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3368,7 +3421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3394,7 +3447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3420,7 +3473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3446,7 +3499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3472,7 +3525,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3498,8 +3551,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="13" t="s">
+    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3524,8 +3577,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="13"/>
+    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="22"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3548,7 +3601,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3574,7 +3627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3600,7 +3653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3626,7 +3679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3652,7 +3705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3678,7 +3731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3704,7 +3757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3730,7 +3783,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -3756,7 +3809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -3782,8 +3835,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="13" t="s">
+    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3808,8 +3861,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="13"/>
+    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="22"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -3832,7 +3885,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -3858,7 +3911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -3884,7 +3937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -3910,7 +3963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -3936,7 +3989,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -3962,7 +4015,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -3988,7 +4041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4014,7 +4067,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4040,7 +4093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4066,7 +4119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4092,7 +4145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4118,7 +4171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4144,7 +4197,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4168,7 +4221,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4194,7 +4247,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4220,7 +4273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4246,7 +4299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4272,7 +4325,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4298,7 +4351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4324,7 +4377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4350,7 +4403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4376,7 +4429,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4402,7 +4455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4428,7 +4481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4454,7 +4507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4480,8 +4533,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="13" t="s">
+    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A145" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4506,8 +4559,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="13"/>
+    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A146" s="22"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4530,7 +4583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4556,7 +4609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4582,7 +4635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4608,7 +4661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4634,7 +4687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4660,7 +4713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4686,7 +4739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4712,7 +4765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4738,7 +4791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -4764,7 +4817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -4790,7 +4843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -4816,7 +4869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -4842,8 +4895,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="13" t="s">
+    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A160" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -4868,8 +4921,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="13"/>
+    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A161" s="22"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -4892,7 +4945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -4918,7 +4971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -4944,7 +4997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -4970,7 +5023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -4996,7 +5049,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5022,7 +5075,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5048,7 +5101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5074,7 +5127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5100,7 +5153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5126,7 +5179,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5152,7 +5205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5178,7 +5231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5204,8 +5257,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="13" t="s">
+    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A175" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5230,8 +5283,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="13"/>
+    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A176" s="22"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5254,7 +5307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5280,7 +5333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5306,7 +5359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5332,7 +5385,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5358,7 +5411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5384,7 +5437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5410,7 +5463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5436,7 +5489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5462,7 +5515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5488,7 +5541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5514,7 +5567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5540,7 +5593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5566,8 +5619,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="13" t="s">
+    <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A190" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5592,8 +5645,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="13"/>
+    <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A191" s="22"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5616,34 +5669,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B192" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C192" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D192" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E192" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F192" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G192" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="H192" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A193" s="21" t="s">
+      <c r="B192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G192" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H192" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B193" s="4" t="s">
@@ -5661,15 +5714,15 @@
       <c r="F193" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G193" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H193" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A194" s="21" t="s">
+      <c r="G193" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H193" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
       <c r="B194" s="4" t="s">
@@ -5687,15 +5740,15 @@
       <c r="F194" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G194" s="20" t="s">
+      <c r="G194" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A195" s="21" t="s">
+    <row r="195" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B195" s="4" t="s">
@@ -5713,41 +5766,41 @@
       <c r="F195" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G195" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="H195" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" s="22" t="s">
+      <c r="G195" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H195" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B196" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C196" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D196" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F196" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G196" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H196" s="19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A197" s="23" t="s">
+      <c r="B196" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G196" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H196" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B197" s="4" t="s">
@@ -5759,47 +5812,47 @@
       <c r="D197" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E197" s="24" t="s">
+      <c r="E197" s="19" t="s">
         <v>35</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G197" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H197" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A198" s="22" t="s">
+      <c r="G197" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H197" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B198" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C198" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D198" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F198" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G198" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H198" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A199" s="21" t="s">
+      <c r="B198" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D198" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F198" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
       <c r="B199" s="4" t="s">
@@ -5814,18 +5867,18 @@
       <c r="E199" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F199" s="24" t="s">
+      <c r="F199" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G199" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H199" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="21" t="s">
+      <c r="G199" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H199" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B200" s="4" t="s">
@@ -5843,14 +5896,14 @@
       <c r="F200" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G200" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H200" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G200" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H200" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -5872,12 +5925,12 @@
       <c r="G201" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H201" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A202" s="21" t="s">
+      <c r="H201" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
       <c r="B202" s="4" t="s">
@@ -5895,41 +5948,46 @@
       <c r="F202" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G202" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H202" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G202" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H202" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B203" s="25" t="s">
+      <c r="B203" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C203" s="25" t="s">
+      <c r="C203" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D203" s="25" t="s">
+      <c r="D203" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E203" s="25" t="s">
+      <c r="E203" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F203" s="25" t="s">
+      <c r="F203" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G203" s="26" t="s">
+      <c r="G203" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H203" s="26" t="s">
+      <c r="H203" s="21" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
@@ -5938,20 +5996,36 @@
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="A79:A80"/>
     <mergeCell ref="A175:A176"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -6152,27 +6226,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6189,23 +6262,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA25835-168D-4574-A6FF-3D390CF48E67}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="43">
   <si>
     <t>GESTOR</t>
   </si>
@@ -148,6 +148,27 @@
   <si>
     <t>Dia de Votación</t>
   </si>
+  <si>
+    <t>6am - 12pm / 4:30pm - 5:30pm</t>
+  </si>
+  <si>
+    <t>7am - 3pm</t>
+  </si>
+  <si>
+    <t>6am - 11am / 7pm - 9pm</t>
+  </si>
+  <si>
+    <t>1pm - 6pm / 9pm - 11pm</t>
+  </si>
+  <si>
+    <t>Incapacidad</t>
+  </si>
+  <si>
+    <t>11am - 7pm</t>
+  </si>
+  <si>
+    <t>1pm - 9pm</t>
+  </si>
 </sst>
 </file>
 
@@ -243,7 +264,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,6 +328,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -436,6 +463,45 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -839,18 +905,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O203"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O232"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -896,8 +963,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="26"/>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="39"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -941,7 +1008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -988,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1035,7 +1102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1082,7 +1149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1129,7 +1196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1176,7 +1243,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1223,7 +1290,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1270,7 +1337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1317,7 +1384,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1364,7 +1431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1411,8 +1478,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="25" t="s">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1437,8 +1504,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="39"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1461,7 +1528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1487,7 +1554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1513,7 +1580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1539,7 +1606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1565,7 +1632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1591,7 +1658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1617,7 +1684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1643,7 +1710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1669,7 +1736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1695,7 +1762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1721,8 +1788,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1747,8 +1814,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="39"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1771,7 +1838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1797,7 +1864,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1823,7 +1890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1849,7 +1916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1875,7 +1942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1901,7 +1968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1927,7 +1994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1953,7 +2020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1979,7 +2046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2005,7 +2072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2031,8 +2098,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2057,8 +2124,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="22"/>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="35"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2081,7 +2148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2107,7 +2174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2133,7 +2200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2159,7 +2226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2185,7 +2252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2211,7 +2278,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2237,7 +2304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2263,7 +2330,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2289,7 +2356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2315,7 +2382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2341,8 +2408,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="22" t="s">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2367,8 +2434,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="22"/>
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="35"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2391,7 +2458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2417,7 +2484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2443,7 +2510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2469,7 +2536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2495,7 +2562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2521,7 +2588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2547,7 +2614,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2573,7 +2640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2599,7 +2666,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2625,7 +2692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2651,8 +2718,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="22" t="s">
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2677,8 +2744,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="22"/>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="35"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2701,7 +2768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2727,7 +2794,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2753,7 +2820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2779,7 +2846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2805,7 +2872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2831,7 +2898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -2857,7 +2924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2883,7 +2950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -2909,7 +2976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -2935,7 +3002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -2961,8 +3028,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="22" t="s">
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -2987,8 +3054,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="22"/>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="35"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3011,7 +3078,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3037,7 +3104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3063,7 +3130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3089,7 +3156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3108,10 +3175,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="23"/>
-      <c r="H84" s="24"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G84" s="36"/>
+      <c r="H84" s="37"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3137,7 +3204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3163,7 +3230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3189,7 +3256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3215,7 +3282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3241,7 +3308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3267,8 +3334,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="22" t="s">
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3293,8 +3360,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="22"/>
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="35"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3317,7 +3384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3343,7 +3410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3369,7 +3436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3395,7 +3462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3421,7 +3488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3447,7 +3514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3473,7 +3540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3499,7 +3566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3525,7 +3592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3551,8 +3618,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="22" t="s">
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3577,8 +3644,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="22"/>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="35"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3601,7 +3668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3627,7 +3694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3653,7 +3720,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3679,7 +3746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3705,7 +3772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3731,7 +3798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3757,7 +3824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3783,7 +3850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -3809,7 +3876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -3835,8 +3902,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="22" t="s">
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3861,8 +3928,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="22"/>
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="35"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -3885,7 +3952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -3911,7 +3978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -3937,7 +4004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -3963,7 +4030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -3989,7 +4056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4015,7 +4082,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4041,7 +4108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4067,7 +4134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4093,7 +4160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4119,7 +4186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4145,7 +4212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4171,7 +4238,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4197,7 +4264,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4221,7 +4288,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4247,7 +4314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4273,7 +4340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4299,7 +4366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4325,7 +4392,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4351,7 +4418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4377,7 +4444,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4403,7 +4470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4429,7 +4496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4455,7 +4522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4481,7 +4548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4507,7 +4574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4533,8 +4600,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="22" t="s">
+    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4559,8 +4626,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="22"/>
+    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A146" s="35"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4583,7 +4650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4609,7 +4676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4635,7 +4702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4661,7 +4728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4687,7 +4754,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4713,7 +4780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4739,7 +4806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4765,7 +4832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4791,7 +4858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -4817,7 +4884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -4843,7 +4910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -4869,7 +4936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -4895,8 +4962,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="22" t="s">
+    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -4921,8 +4988,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="22"/>
+    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="35"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -4945,7 +5012,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -4971,7 +5038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -4997,7 +5064,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5023,7 +5090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5049,7 +5116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5075,7 +5142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5101,7 +5168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5127,7 +5194,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5153,7 +5220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5179,7 +5246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5205,7 +5272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5231,7 +5298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5257,8 +5324,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="22" t="s">
+    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5283,8 +5350,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="22"/>
+    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="35"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5307,7 +5374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5333,7 +5400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5359,7 +5426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5385,7 +5452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5411,7 +5478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5437,7 +5504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5463,7 +5530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5489,7 +5556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5515,7 +5582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5541,7 +5608,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5567,7 +5634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5593,7 +5660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5619,8 +5686,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="22" t="s">
+    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A190" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5645,8 +5712,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="22"/>
+    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A191" s="35"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5669,7 +5736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5695,7 +5762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5721,7 +5788,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5747,7 +5814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -5773,7 +5840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -5799,7 +5866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -5825,7 +5892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -5851,7 +5918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -5877,7 +5944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -5903,7 +5970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -5929,7 +5996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -5955,7 +6022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -5981,13 +6048,707 @@
         <v>34</v>
       </c>
     </row>
+    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A205" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="22">
+        <v>46237</v>
+      </c>
+      <c r="C205" s="22">
+        <v>46238</v>
+      </c>
+      <c r="D205" s="22">
+        <v>46239</v>
+      </c>
+      <c r="E205" s="22">
+        <v>46240</v>
+      </c>
+      <c r="F205" s="22">
+        <v>46241</v>
+      </c>
+      <c r="G205" s="22">
+        <v>46242</v>
+      </c>
+      <c r="H205" s="22">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A206" s="34"/>
+      <c r="B206" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C206" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D206" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E206" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F206" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G206" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H206" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A207" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G207" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H207" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A208" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H208" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A209" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B209" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D209" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F209" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G209" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H209" s="26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A210" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H210" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A211" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B211" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D211" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E211" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F211" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G211" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H211" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A212" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B212" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C212" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D212" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E212" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F212" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G212" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H212" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A213" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H213" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A214" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A215" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H215" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A216" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H216" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A217" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B217" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C217" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D217" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E217" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F217" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H217" s="29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A218" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B218" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C218" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D218" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E218" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F218" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H218" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
+      <c r="C219" s="30"/>
+      <c r="D219" s="30"/>
+      <c r="E219" s="30"/>
+      <c r="F219" s="30"/>
+      <c r="G219" s="30"/>
+      <c r="H219" s="30"/>
+    </row>
+    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A220" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B220" s="22">
+        <v>46244</v>
+      </c>
+      <c r="C220" s="22">
+        <v>46245</v>
+      </c>
+      <c r="D220" s="22">
+        <v>46246</v>
+      </c>
+      <c r="E220" s="22">
+        <v>46247</v>
+      </c>
+      <c r="F220" s="22">
+        <v>46248</v>
+      </c>
+      <c r="G220" s="22">
+        <v>46249</v>
+      </c>
+      <c r="H220" s="22">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A221" s="34"/>
+      <c r="B221" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C221" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D221" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E221" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F221" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G221" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H221" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A222" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H222" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A223" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G223" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H223" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A224" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G224" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H224" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A225" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F225" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="G225" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H225" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A226" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B226" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C226" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D226" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F226" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G226" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H226" s="32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A227" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B227" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C227" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D227" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E227" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F227" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G227" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A228" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H228" s="26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A229" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H229" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A230" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B230" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D230" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F230" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G230" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H230" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A231" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B231" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C231" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D231" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E231" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F231" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H231" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
+      <c r="C232" s="30"/>
+      <c r="D232" s="30"/>
+      <c r="E232" s="30"/>
+      <c r="F232" s="30"/>
+      <c r="G232" s="30"/>
+      <c r="H232" s="30"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A220:A221"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA25835-168D-4574-A6FF-3D390CF48E67}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B29E68B-1F2A-40C9-81A6-E5BA0A2D555C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="45">
   <si>
     <t>GESTOR</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>1pm - 9pm</t>
+  </si>
+  <si>
+    <t>8am - 4pm - 1/2 día de Votación</t>
+  </si>
+  <si>
+    <t>11am - 7pm - 1/2 día de Votación</t>
   </si>
 </sst>
 </file>
@@ -418,7 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -481,9 +487,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -497,13 +500,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -511,11 +520,11 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -905,19 +914,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O232"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O233"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -963,8 +972,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="33"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1008,7 +1017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1055,7 +1064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1102,7 +1111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1149,7 +1158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1196,7 +1205,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1243,7 +1252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1290,7 +1299,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1337,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1384,7 +1393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1431,7 +1440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1478,8 +1487,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1504,8 +1513,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="33"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1528,7 +1537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1554,7 +1563,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1580,7 +1589,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1606,7 +1615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1632,7 +1641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1658,7 +1667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1684,7 +1693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1710,7 +1719,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1736,7 +1745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1762,7 +1771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1788,8 +1797,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1814,8 +1823,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="39"/>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="33"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1838,7 +1847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1864,7 +1873,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1890,7 +1899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1916,7 +1925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1942,7 +1951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1968,7 +1977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1994,7 +2003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2020,7 +2029,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2046,7 +2055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2072,7 +2081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2098,8 +2107,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="35" t="s">
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2124,8 +2133,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="34"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2148,7 +2157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2174,7 +2183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2200,7 +2209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2226,7 +2235,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2252,7 +2261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2278,7 +2287,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2304,7 +2313,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2330,7 +2339,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2356,7 +2365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2382,7 +2391,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2408,8 +2417,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="35" t="s">
+    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2434,8 +2443,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="35"/>
+    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="34"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2458,7 +2467,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2484,7 +2493,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2510,7 +2519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2536,7 +2545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2562,7 +2571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2588,7 +2597,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2614,7 +2623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2640,7 +2649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2666,7 +2675,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2692,7 +2701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2718,8 +2727,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="35" t="s">
+    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2744,8 +2753,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="35"/>
+    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="34"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2768,7 +2777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2794,7 +2803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2820,7 +2829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2846,7 +2855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2872,7 +2881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2898,7 +2907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -2924,7 +2933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2950,7 +2959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -2976,7 +2985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3002,7 +3011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3028,8 +3037,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
+    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3054,8 +3063,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="35"/>
+    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="34"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3078,7 +3087,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3104,7 +3113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3130,7 +3139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3156,7 +3165,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3175,10 +3184,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="36"/>
-      <c r="H84" s="37"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G84" s="37"/>
+      <c r="H84" s="38"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3204,7 +3213,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3230,7 +3239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3256,7 +3265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3282,7 +3291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3308,7 +3317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3334,8 +3343,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="35" t="s">
+    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3360,8 +3369,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="35"/>
+    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="34"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3384,7 +3393,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3410,7 +3419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3436,7 +3445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3462,7 +3471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3488,7 +3497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3514,7 +3523,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3540,7 +3549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3566,7 +3575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3592,7 +3601,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3618,8 +3627,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="35" t="s">
+    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3644,8 +3653,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="35"/>
+    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="34"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3668,7 +3677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3694,7 +3703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3720,7 +3729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3746,7 +3755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3772,7 +3781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3798,7 +3807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3824,7 +3833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3850,7 +3859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -3876,7 +3885,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -3902,8 +3911,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="35" t="s">
+    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3928,8 +3937,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="35"/>
+    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="34"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -3952,7 +3961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -3978,7 +3987,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4004,7 +4013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4030,7 +4039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4056,7 +4065,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4082,7 +4091,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4108,7 +4117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4134,7 +4143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4160,7 +4169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4186,7 +4195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4212,7 +4221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4238,7 +4247,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4264,7 +4273,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4288,7 +4297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4314,7 +4323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4340,7 +4349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4366,7 +4375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4392,7 +4401,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4418,7 +4427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4444,7 +4453,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4470,7 +4479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4496,7 +4505,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4522,7 +4531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4548,7 +4557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4574,7 +4583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4600,8 +4609,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="35" t="s">
+    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A145" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4626,8 +4635,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="35"/>
+    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A146" s="34"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4650,7 +4659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4676,7 +4685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4702,7 +4711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4728,7 +4737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4754,7 +4763,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4780,7 +4789,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4806,7 +4815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4832,7 +4841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4858,7 +4867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -4884,7 +4893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -4910,7 +4919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -4936,7 +4945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -4962,8 +4971,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="35" t="s">
+    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A160" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -4988,8 +4997,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="35"/>
+    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A161" s="34"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5012,7 +5021,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5038,7 +5047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5064,7 +5073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5090,7 +5099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5116,7 +5125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5142,7 +5151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5168,7 +5177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5194,7 +5203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5220,7 +5229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5246,7 +5255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5272,7 +5281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5298,7 +5307,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5324,8 +5333,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="35" t="s">
+    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A175" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5350,8 +5359,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="35"/>
+    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A176" s="34"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5374,7 +5383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5400,7 +5409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5426,7 +5435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5452,7 +5461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5478,7 +5487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5504,7 +5513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5530,7 +5539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5556,7 +5565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5582,7 +5591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5608,7 +5617,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5634,7 +5643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5660,7 +5669,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5686,8 +5695,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="35" t="s">
+    <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A190" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5712,8 +5721,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="35"/>
+    <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A191" s="34"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5736,7 +5745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5762,7 +5771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5788,7 +5797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5814,7 +5823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -5840,7 +5849,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -5866,7 +5875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -5892,7 +5901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -5918,7 +5927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -5944,7 +5953,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -5970,7 +5979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -5996,7 +6005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6022,7 +6031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6048,8 +6057,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="33" t="s">
+    <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A205" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="22">
@@ -6074,8 +6083,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="34"/>
+    <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A206" s="36"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6098,7 +6107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6124,7 +6133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6150,7 +6159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6160,8 +6169,8 @@
       <c r="C209" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D209" s="24" t="s">
-        <v>9</v>
+      <c r="D209" s="39" t="s">
+        <v>43</v>
       </c>
       <c r="E209" s="26" t="s">
         <v>19</v>
@@ -6176,7 +6185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6202,7 +6211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6228,7 +6237,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6241,20 +6250,20 @@
       <c r="D212" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E212" s="24" t="s">
-        <v>41</v>
+      <c r="E212" s="39" t="s">
+        <v>44</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G212" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H212" s="24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="G212" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H212" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6273,14 +6282,14 @@
       <c r="F213" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="G213" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="H213" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G213" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H213" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6306,7 +6315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6332,7 +6341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6349,46 +6358,46 @@
         <v>13</v>
       </c>
       <c r="F216" s="24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G216" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H216" s="25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B217" s="28" t="s">
+      <c r="B217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C217" s="28" t="s">
+      <c r="C217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D217" s="28" t="s">
+      <c r="D217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E217" s="28" t="s">
+      <c r="E217" s="24" t="s">
         <v>31</v>
       </c>
       <c r="F217" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G217" s="29" t="s">
+      <c r="G217" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H217" s="29" t="s">
+      <c r="H217" s="28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B218" s="19" t="s">
+      <c r="B218" s="40" t="s">
         <v>35</v>
       </c>
       <c r="C218" s="26" t="s">
@@ -6410,18 +6419,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
-      <c r="C219" s="30"/>
-      <c r="D219" s="30"/>
-      <c r="E219" s="30"/>
-      <c r="F219" s="30"/>
-      <c r="G219" s="30"/>
-      <c r="H219" s="30"/>
-    </row>
-    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="33" t="s">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
+      <c r="C219" s="29"/>
+      <c r="D219" s="29"/>
+      <c r="E219" s="29"/>
+      <c r="F219" s="29"/>
+      <c r="G219" s="29"/>
+      <c r="H219" s="29"/>
+    </row>
+    <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A220" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="22">
@@ -6446,8 +6455,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="34"/>
+    <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A221" s="36"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6470,7 +6479,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6496,7 +6505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6522,9 +6531,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="23" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B224" s="24" t="s">
         <v>9</v>
@@ -6545,10 +6554,10 @@
         <v>10</v>
       </c>
       <c r="H224" s="24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6564,17 +6573,17 @@
       <c r="E225" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F225" s="31" t="s">
+      <c r="F225" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="G225" s="31" t="s">
+      <c r="G225" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="H225" s="31" t="s">
+      <c r="H225" s="30" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="23" t="s">
         <v>18</v>
       </c>
@@ -6596,11 +6605,11 @@
       <c r="G226" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="H226" s="32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="H226" s="31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A227" s="23" t="s">
         <v>17</v>
       </c>
@@ -6626,59 +6635,59 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H228" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A229" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G228" s="26" t="s">
+      <c r="B229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H228" s="26" t="s">
+      <c r="H229" s="26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A229" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G229" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H229" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="23" t="s">
         <v>20</v>
       </c>
@@ -6694,8 +6703,8 @@
       <c r="E230" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F230" s="24" t="s">
-        <v>11</v>
+      <c r="F230" s="40" t="s">
+        <v>35</v>
       </c>
       <c r="G230" s="25" t="s">
         <v>10</v>
@@ -6704,9 +6713,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B231" s="24" t="s">
         <v>13</v>
@@ -6730,23 +6739,60 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
-      <c r="C232" s="30"/>
-      <c r="D232" s="30"/>
-      <c r="E232" s="30"/>
-      <c r="F232" s="30"/>
-      <c r="G232" s="30"/>
-      <c r="H232" s="30"/>
+    <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A232" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B232" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C232" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D232" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E232" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F232" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G232" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H232" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A233" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B233" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D233" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F233" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G233" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H233" s="28" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A190:A191"/>
@@ -6759,6 +6805,11 @@
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6767,6 +6818,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
@@ -6775,15 +6835,6 @@
     <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6988,20 +7039,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
     <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B29E68B-1F2A-40C9-81A6-E5BA0A2D555C}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE51109-7016-4FEF-BF2C-19B9330DBB34}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -180,7 +180,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +271,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -420,9 +430,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -469,35 +482,23 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -505,20 +506,32 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -527,9 +540,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
     <cellStyle name="20% - Énfasis4" xfId="1" builtinId="42"/>
+    <cellStyle name="Millares 2" xfId="3" xr:uid="{BF0B93C0-BEA2-4B38-8FEC-CCC1230B4CED}"/>
+    <cellStyle name="Millares 3" xfId="4" xr:uid="{3491A9D1-8125-400A-9FF6-DAC3878D5F73}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{7F0E0DEF-3BEC-4094-B945-A7AA33DB835B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -926,7 +942,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -973,7 +989,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="33"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1488,7 +1504,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1514,7 +1530,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1798,7 +1814,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1824,7 +1840,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2108,7 +2124,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="34" t="s">
+      <c r="A40" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2134,7 +2150,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="34"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2418,7 +2434,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="34" t="s">
+      <c r="A53" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2444,7 +2460,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="34"/>
+      <c r="A54" s="25"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2728,7 +2744,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="34" t="s">
+      <c r="A66" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2754,7 +2770,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="34"/>
+      <c r="A67" s="25"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3038,7 +3054,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="34" t="s">
+      <c r="A79" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3064,7 +3080,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="34"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3184,8 +3200,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="37"/>
-      <c r="H84" s="38"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="27"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -3344,7 +3360,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="34" t="s">
+      <c r="A92" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3370,7 +3386,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="34"/>
+      <c r="A93" s="25"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3628,7 +3644,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="34" t="s">
+      <c r="A104" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3654,7 +3670,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="34"/>
+      <c r="A105" s="25"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3912,7 +3928,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="34" t="s">
+      <c r="A116" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3938,7 +3954,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="34"/>
+      <c r="A117" s="25"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4610,7 +4626,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="34" t="s">
+      <c r="A145" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4636,7 +4652,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="34"/>
+      <c r="A146" s="25"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4972,7 +4988,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="34" t="s">
+      <c r="A160" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -4998,7 +5014,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="34"/>
+      <c r="A161" s="25"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5334,7 +5350,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="34" t="s">
+      <c r="A175" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5360,7 +5376,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="34"/>
+      <c r="A176" s="25"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5696,7 +5712,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="34" t="s">
+      <c r="A190" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5722,7 +5738,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="34"/>
+      <c r="A191" s="25"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6058,551 +6074,551 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="35" t="s">
+      <c r="A205" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B205" s="22">
+      <c r="B205" s="34">
         <v>46237</v>
       </c>
-      <c r="C205" s="22">
+      <c r="C205" s="34">
         <v>46238</v>
       </c>
-      <c r="D205" s="22">
+      <c r="D205" s="34">
         <v>46239</v>
       </c>
-      <c r="E205" s="22">
+      <c r="E205" s="34">
         <v>46240</v>
       </c>
-      <c r="F205" s="22">
+      <c r="F205" s="34">
         <v>46241</v>
       </c>
-      <c r="G205" s="22">
+      <c r="G205" s="34">
         <v>46242</v>
       </c>
-      <c r="H205" s="22">
+      <c r="H205" s="34">
         <v>46243</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="36"/>
-      <c r="B206" s="23" t="s">
+      <c r="A206" s="24"/>
+      <c r="B206" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C206" s="23" t="s">
+      <c r="C206" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D206" s="23" t="s">
+      <c r="D206" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E206" s="23" t="s">
+      <c r="E206" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F206" s="23" t="s">
+      <c r="F206" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G206" s="23" t="s">
+      <c r="G206" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H206" s="23" t="s">
+      <c r="H206" s="30" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A207" s="23" t="s">
+      <c r="A207" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B207" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C207" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D207" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E207" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F207" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G207" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H207" s="24" t="s">
+      <c r="B207" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C207" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F207" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G207" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H207" s="32" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A208" s="23" t="s">
+      <c r="A208" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B208" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C208" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D208" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E208" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F208" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G208" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="H208" s="25" t="s">
+      <c r="B208" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C208" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D208" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F208" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G208" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H208" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A209" s="23" t="s">
+      <c r="A209" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B209" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C209" s="24" t="s">
+      <c r="B209" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="32" t="s">
         <v>9</v>
       </c>
       <c r="D209" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="E209" s="26" t="s">
+      <c r="E209" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F209" s="26" t="s">
+      <c r="F209" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G209" s="26" t="s">
+      <c r="G209" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H209" s="26" t="s">
+      <c r="H209" s="33" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A210" s="23" t="s">
+      <c r="A210" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B210" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C210" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D210" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E210" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F210" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G210" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="H210" s="25" t="s">
+      <c r="B210" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G210" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H210" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A211" s="23" t="s">
+      <c r="A211" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B211" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C211" s="24" t="s">
+      <c r="B211" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D211" s="24" t="s">
+      <c r="D211" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E211" s="24" t="s">
+      <c r="E211" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F211" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G211" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H211" s="24" t="s">
+      <c r="F211" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G211" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H211" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A212" s="23" t="s">
+      <c r="A212" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B212" s="24" t="s">
+      <c r="B212" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C212" s="24" t="s">
+      <c r="C212" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D212" s="24" t="s">
+      <c r="D212" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E212" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="F212" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G212" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H212" s="25" t="s">
+      <c r="F212" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G212" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H212" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A213" s="23" t="s">
+      <c r="A213" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B213" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C213" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D213" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F213" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G213" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H213" s="24" t="s">
+      <c r="B213" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D213" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F213" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H213" s="32" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A214" s="23" t="s">
+      <c r="A214" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B214" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C214" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D214" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E214" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F214" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G214" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="H214" s="25" t="s">
+      <c r="B214" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D214" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F214" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A215" s="23" t="s">
+      <c r="A215" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B215" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C215" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D215" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F215" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G215" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H215" s="24" t="s">
+      <c r="B215" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F215" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H215" s="32" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A216" s="23" t="s">
+      <c r="A216" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B216" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C216" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D216" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E216" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F216" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G216" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="H216" s="25" t="s">
+      <c r="B216" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C216" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D216" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F216" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G216" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A217" s="27" t="s">
+      <c r="A217" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B217" s="24" t="s">
+      <c r="B217" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C217" s="24" t="s">
+      <c r="C217" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D217" s="24" t="s">
+      <c r="D217" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="E217" s="24" t="s">
+      <c r="E217" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F217" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G217" s="28" t="s">
+      <c r="F217" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="H217" s="28" t="s">
+      <c r="H217" s="38" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A218" s="23" t="s">
+      <c r="A218" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B218" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C218" s="26" t="s">
+      <c r="C218" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D218" s="26" t="s">
+      <c r="D218" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E218" s="26" t="s">
+      <c r="E218" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F218" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G218" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H218" s="25" t="s">
+      <c r="F218" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H218" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
-      <c r="C219" s="29"/>
-      <c r="D219" s="29"/>
-      <c r="E219" s="29"/>
-      <c r="F219" s="29"/>
-      <c r="G219" s="29"/>
-      <c r="H219" s="29"/>
+      <c r="A219" s="22"/>
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="22"/>
+      <c r="E219" s="22"/>
+      <c r="F219" s="22"/>
+      <c r="G219" s="22"/>
+      <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="35" t="s">
+      <c r="A220" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B220" s="22">
+      <c r="B220" s="34">
         <v>46244</v>
       </c>
-      <c r="C220" s="22">
+      <c r="C220" s="34">
         <v>46245</v>
       </c>
-      <c r="D220" s="22">
+      <c r="D220" s="34">
         <v>46246</v>
       </c>
-      <c r="E220" s="22">
+      <c r="E220" s="34">
         <v>46247</v>
       </c>
-      <c r="F220" s="22">
+      <c r="F220" s="34">
         <v>46248</v>
       </c>
-      <c r="G220" s="22">
+      <c r="G220" s="34">
         <v>46249</v>
       </c>
-      <c r="H220" s="22">
+      <c r="H220" s="34">
         <v>46250</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="36"/>
-      <c r="B221" s="23" t="s">
+      <c r="A221" s="24"/>
+      <c r="B221" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C221" s="23" t="s">
+      <c r="C221" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D221" s="23" t="s">
+      <c r="D221" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E221" s="23" t="s">
+      <c r="E221" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F221" s="23" t="s">
+      <c r="F221" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G221" s="23" t="s">
+      <c r="G221" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H221" s="23" t="s">
+      <c r="H221" s="30" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A222" s="23" t="s">
+      <c r="A222" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B222" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C222" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D222" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E222" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F222" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G222" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="H222" s="25" t="s">
+      <c r="B222" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C222" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F222" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G222" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H222" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A223" s="23" t="s">
+      <c r="A223" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B223" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C223" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D223" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E223" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F223" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G223" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H223" s="24" t="s">
+      <c r="B223" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C223" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F223" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G223" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H223" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A224" s="23" t="s">
+      <c r="A224" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B224" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C224" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D224" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E224" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F224" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G224" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H224" s="24" t="s">
+      <c r="B224" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C224" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D224" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F224" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G224" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H224" s="32" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A225" s="23" t="s">
+      <c r="A225" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B225" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C225" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D225" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E225" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F225" s="30" t="s">
+      <c r="B225" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F225" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="G225" s="30" t="s">
+      <c r="G225" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="H225" s="30" t="s">
+      <c r="H225" s="36" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A226" s="23" t="s">
+      <c r="A226" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B226" s="26" t="s">
+      <c r="B226" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C226" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D226" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E226" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F226" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G226" s="24" t="s">
+      <c r="C226" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D226" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F226" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G226" s="32" t="s">
         <v>26</v>
       </c>
       <c r="H226" s="31" t="s">
@@ -6610,191 +6626,194 @@
       </c>
     </row>
     <row r="227" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A227" s="23" t="s">
+      <c r="A227" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B227" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C227" s="24" t="s">
+      <c r="B227" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C227" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D227" s="24" t="s">
+      <c r="D227" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E227" s="24" t="s">
+      <c r="E227" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F227" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G227" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="H227" s="25" t="s">
+      <c r="F227" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G227" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A228" s="23" t="s">
+      <c r="A228" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F228" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G228" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H228" s="24" t="s">
+      <c r="B228" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H228" s="32" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A229" s="23" t="s">
+      <c r="A229" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F229" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G229" s="26" t="s">
+      <c r="B229" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D229" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H229" s="26" t="s">
+      <c r="H229" s="33" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A230" s="23" t="s">
+      <c r="A230" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B230" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C230" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D230" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E230" s="24" t="s">
+      <c r="B230" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D230" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="32" t="s">
         <v>11</v>
       </c>
       <c r="F230" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="G230" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H230" s="24" t="s">
+      <c r="G230" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H230" s="32" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A231" s="23" t="s">
+      <c r="A231" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B231" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C231" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D231" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E231" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F231" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G231" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H231" s="25" t="s">
+      <c r="B231" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C231" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D231" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E231" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F231" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H231" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A232" s="27" t="s">
+      <c r="A232" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B232" s="24" t="s">
+      <c r="B232" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C232" s="24" t="s">
+      <c r="C232" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D232" s="24" t="s">
+      <c r="D232" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="E232" s="24" t="s">
+      <c r="E232" s="32" t="s">
         <v>31</v>
       </c>
       <c r="F232" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="G232" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H232" s="25" t="s">
+      <c r="G232" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H232" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A233" s="23" t="s">
+      <c r="A233" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B233" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C233" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D233" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E233" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F233" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G233" s="28" t="s">
+      <c r="B233" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C233" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D233" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E233" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="F233" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G233" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="H233" s="28" t="s">
+      <c r="H233" s="38" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
@@ -6805,11 +6824,8 @@
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A205:A206"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6818,26 +6834,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -7038,10 +7034,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7058,20 +7085,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE51109-7016-4FEF-BF2C-19B9330DBB34}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FBA5BF-47C2-406C-AC55-13C51F6A0428}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -181,9 +181,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +279,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -354,7 +377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -429,15 +452,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -485,31 +519,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -538,6 +548,66 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -611,6 +681,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -942,7 +1016,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -989,7 +1063,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
+      <c r="A2" s="34"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1504,7 +1578,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1530,7 +1604,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="29"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1814,7 +1888,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1840,7 +1914,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="29"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2124,7 +2198,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2150,7 +2224,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="25"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2434,7 +2508,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2460,7 +2534,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="25"/>
+      <c r="A54" s="35"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2744,7 +2818,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="25" t="s">
+      <c r="A66" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2770,7 +2844,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="25"/>
+      <c r="A67" s="35"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3054,7 +3128,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="25" t="s">
+      <c r="A79" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3080,7 +3154,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="25"/>
+      <c r="A80" s="35"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3200,8 +3274,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="26"/>
-      <c r="H84" s="27"/>
+      <c r="G84" s="36"/>
+      <c r="H84" s="37"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -3360,7 +3434,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="25" t="s">
+      <c r="A92" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3386,7 +3460,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="25"/>
+      <c r="A93" s="35"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3644,7 +3718,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="25" t="s">
+      <c r="A104" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3670,7 +3744,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="25"/>
+      <c r="A105" s="35"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3928,7 +4002,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="25" t="s">
+      <c r="A116" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -3954,7 +4028,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="25"/>
+      <c r="A117" s="35"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4626,7 +4700,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="25" t="s">
+      <c r="A145" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4652,7 +4726,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="25"/>
+      <c r="A146" s="35"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4988,7 +5062,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="25" t="s">
+      <c r="A160" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5014,7 +5088,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="25"/>
+      <c r="A161" s="35"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5350,7 +5424,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="25" t="s">
+      <c r="A175" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5376,7 +5450,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="25"/>
+      <c r="A176" s="35"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5712,7 +5786,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="25" t="s">
+      <c r="A190" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5738,7 +5812,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="25"/>
+      <c r="A191" s="35"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6074,364 +6148,364 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="23" t="s">
+      <c r="A205" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B205" s="34">
+      <c r="B205" s="26">
         <v>46237</v>
       </c>
-      <c r="C205" s="34">
+      <c r="C205" s="26">
         <v>46238</v>
       </c>
-      <c r="D205" s="34">
+      <c r="D205" s="26">
         <v>46239</v>
       </c>
-      <c r="E205" s="34">
+      <c r="E205" s="26">
         <v>46240</v>
       </c>
-      <c r="F205" s="34">
+      <c r="F205" s="26">
         <v>46241</v>
       </c>
-      <c r="G205" s="34">
+      <c r="G205" s="26">
         <v>46242</v>
       </c>
-      <c r="H205" s="34">
+      <c r="H205" s="26">
         <v>46243</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="24"/>
-      <c r="B206" s="30" t="s">
+      <c r="A206" s="38"/>
+      <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C206" s="30" t="s">
+      <c r="C206" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D206" s="30" t="s">
+      <c r="D206" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E206" s="30" t="s">
+      <c r="E206" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F206" s="30" t="s">
+      <c r="F206" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G206" s="30" t="s">
+      <c r="G206" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H206" s="30" t="s">
+      <c r="H206" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A207" s="30" t="s">
+      <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B207" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C207" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D207" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E207" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F207" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G207" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H207" s="32" t="s">
+      <c r="B207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F207" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G207" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H207" s="24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A208" s="30" t="s">
+      <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B208" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C208" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D208" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E208" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F208" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G208" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H208" s="37" t="s">
+      <c r="B208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G208" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H208" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A209" s="30" t="s">
+      <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B209" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C209" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D209" s="39" t="s">
+      <c r="B209" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D209" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E209" s="33" t="s">
+      <c r="E209" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F209" s="33" t="s">
+      <c r="F209" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="G209" s="33" t="s">
+      <c r="G209" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="H209" s="33" t="s">
+      <c r="H209" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A210" s="30" t="s">
+      <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B210" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C210" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D210" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E210" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F210" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G210" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H210" s="37" t="s">
+      <c r="B210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G210" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H210" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A211" s="30" t="s">
+      <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B211" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C211" s="32" t="s">
+      <c r="B211" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D211" s="32" t="s">
+      <c r="D211" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="E211" s="32" t="s">
+      <c r="E211" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="F211" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G211" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H211" s="32" t="s">
+      <c r="F211" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G211" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H211" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A212" s="30" t="s">
+      <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B212" s="32" t="s">
+      <c r="B212" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C212" s="32" t="s">
+      <c r="C212" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D212" s="32" t="s">
+      <c r="D212" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E212" s="39" t="s">
+      <c r="E212" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="F212" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G212" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H212" s="37" t="s">
+      <c r="F212" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G212" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H212" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A213" s="30" t="s">
+      <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B213" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C213" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D213" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F213" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G213" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H213" s="32" t="s">
+      <c r="B213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F213" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H213" s="24" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A214" s="30" t="s">
+      <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B214" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C214" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D214" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E214" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F214" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G214" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="H214" s="37" t="s">
+      <c r="B214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F214" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H214" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A215" s="30" t="s">
+      <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B215" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C215" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D215" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F215" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G215" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H215" s="32" t="s">
+      <c r="B215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F215" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H215" s="24" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A216" s="30" t="s">
+      <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B216" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C216" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D216" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E216" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F216" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G216" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="H216" s="37" t="s">
+      <c r="B216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F216" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="G216" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A217" s="35" t="s">
+      <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B217" s="32" t="s">
+      <c r="B217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C217" s="32" t="s">
+      <c r="C217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D217" s="32" t="s">
+      <c r="D217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E217" s="32" t="s">
+      <c r="E217" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="F217" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G217" s="38" t="s">
+      <c r="F217" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="H217" s="38" t="s">
+      <c r="G217" s="30" t="s">
         <v>34</v>
       </c>
+      <c r="H217" s="47" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="218" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A218" s="30" t="s">
+      <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B218" s="40" t="s">
+      <c r="B218" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C218" s="33" t="s">
+      <c r="C218" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D218" s="33" t="s">
+      <c r="D218" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E218" s="33" t="s">
+      <c r="E218" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F218" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G218" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H218" s="37" t="s">
+      <c r="F218" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H218" s="49" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6446,374 +6520,371 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="23" t="s">
+      <c r="A220" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B220" s="34">
+      <c r="B220" s="26">
         <v>46244</v>
       </c>
-      <c r="C220" s="34">
+      <c r="C220" s="26">
         <v>46245</v>
       </c>
-      <c r="D220" s="34">
+      <c r="D220" s="26">
         <v>46246</v>
       </c>
-      <c r="E220" s="34">
+      <c r="E220" s="26">
         <v>46247</v>
       </c>
-      <c r="F220" s="34">
+      <c r="F220" s="26">
         <v>46248</v>
       </c>
-      <c r="G220" s="34">
+      <c r="G220" s="26">
         <v>46249</v>
       </c>
-      <c r="H220" s="34">
+      <c r="H220" s="26">
         <v>46250</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="24"/>
-      <c r="B221" s="30" t="s">
+      <c r="A221" s="38"/>
+      <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C221" s="30" t="s">
+      <c r="C221" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D221" s="30" t="s">
+      <c r="D221" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E221" s="30" t="s">
+      <c r="E221" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F221" s="30" t="s">
+      <c r="F221" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G221" s="30" t="s">
+      <c r="G221" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H221" s="30" t="s">
+      <c r="H221" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A222" s="30" t="s">
+      <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B222" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C222" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D222" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E222" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F222" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G222" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H222" s="37" t="s">
+      <c r="B222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C222" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G222" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H222" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A223" s="30" t="s">
+      <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B223" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C223" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D223" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E223" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F223" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G223" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H223" s="32" t="s">
+      <c r="B223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F223" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G223" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H223" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A224" s="30" t="s">
+      <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B224" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C224" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D224" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E224" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F224" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G224" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H224" s="32" t="s">
+      <c r="B224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F224" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G224" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H224" s="24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A225" s="30" t="s">
+      <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B225" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C225" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D225" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E225" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F225" s="36" t="s">
+      <c r="B225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F225" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G225" s="36" t="s">
+      <c r="G225" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="H225" s="36" t="s">
+      <c r="H225" s="28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A226" s="30" t="s">
+    <row r="226" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A226" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B226" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C226" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D226" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E226" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F226" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G226" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H226" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A227" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D227" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F227" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G227" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H227" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A228" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H228" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A229" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G229" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H229" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A230" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B230" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C230" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D230" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E230" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F230" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G230" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H230" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A231" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B226" s="33" t="s">
+      <c r="B231" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C226" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D226" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E226" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F226" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G226" s="32" t="s">
+      <c r="C231" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D231" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F231" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H226" s="31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A227" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B227" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C227" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D227" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="E227" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F227" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G227" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="H227" s="37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A228" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B228" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C228" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D228" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E228" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F228" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G228" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H228" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A229" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B229" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C229" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D229" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E229" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F229" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G229" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H229" s="33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A230" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B230" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C230" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D230" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E230" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F230" s="40" t="s">
+      <c r="H231" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A232" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B232" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C232" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D232" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="E232" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="F232" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G230" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H230" s="32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A231" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B231" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C231" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D231" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E231" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F231" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G231" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H231" s="37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A232" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B232" s="32" t="s">
+      <c r="G232" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="H232" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A233" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B233" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C232" s="32" t="s">
+      <c r="C233" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D232" s="32" t="s">
+      <c r="D233" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E232" s="32" t="s">
+      <c r="E233" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F232" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="G232" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="H232" s="37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A233" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B233" s="32" t="s">
+      <c r="F233" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C233" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D233" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E233" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="F233" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="G233" s="38" t="s">
+      <c r="G233" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="H233" s="38" t="s">
+      <c r="H233" s="47" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A66:A67"/>
@@ -6824,8 +6895,11 @@
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6834,6 +6908,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -7034,27 +7128,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7071,23 +7164,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FBA5BF-47C2-406C-AC55-13C51F6A0428}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C241B4B-405A-4B29-A08D-1D78DC68F8ED}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -471,7 +471,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -549,24 +549,6 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -581,9 +563,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -607,6 +586,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -681,10 +678,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1009,14 +1002,15 @@
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1063,7 +1057,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="34"/>
+      <c r="A2" s="51"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1578,7 +1572,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1604,7 +1598,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="34"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1888,7 +1882,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1914,7 +1908,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="34"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2198,7 +2192,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="35" t="s">
+      <c r="A40" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2224,7 +2218,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="35"/>
+      <c r="A41" s="47"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2508,7 +2502,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="35" t="s">
+      <c r="A53" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2534,7 +2528,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="35"/>
+      <c r="A54" s="47"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2818,7 +2812,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="35" t="s">
+      <c r="A66" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2844,7 +2838,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="35"/>
+      <c r="A67" s="47"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3128,7 +3122,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3154,7 +3148,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="35"/>
+      <c r="A80" s="47"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3274,8 +3268,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="36"/>
-      <c r="H84" s="37"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="49"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -3434,7 +3428,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="35" t="s">
+      <c r="A92" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3460,7 +3454,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="35"/>
+      <c r="A93" s="47"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3718,7 +3712,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="35" t="s">
+      <c r="A104" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3744,7 +3738,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="35"/>
+      <c r="A105" s="47"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4002,7 +3996,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="35" t="s">
+      <c r="A116" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4028,7 +4022,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="35"/>
+      <c r="A117" s="47"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4700,7 +4694,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="35" t="s">
+      <c r="A145" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4726,7 +4720,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="35"/>
+      <c r="A146" s="47"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5062,7 +5056,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="35" t="s">
+      <c r="A160" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5088,7 +5082,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="35"/>
+      <c r="A161" s="47"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5424,7 +5418,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="35" t="s">
+      <c r="A175" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5450,7 +5444,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="35"/>
+      <c r="A176" s="47"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5786,7 +5780,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="35" t="s">
+      <c r="A190" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5812,7 +5806,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="35"/>
+      <c r="A191" s="47"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6148,7 +6142,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="38" t="s">
+      <c r="A205" s="46" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6174,7 +6168,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="38"/>
+      <c r="A206" s="46"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6447,10 +6441,10 @@
       <c r="E216" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F216" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="G216" s="45" t="s">
+      <c r="F216" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="G216" s="38" t="s">
         <v>11</v>
       </c>
       <c r="H216" s="29" t="s">
@@ -6470,16 +6464,16 @@
       <c r="D217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E217" s="46" t="s">
+      <c r="E217" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F217" s="43" t="s">
+      <c r="F217" s="37" t="s">
         <v>34</v>
       </c>
       <c r="G217" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="H217" s="47" t="s">
+      <c r="H217" s="40" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6496,7 +6490,7 @@
       <c r="D218" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E218" s="48" t="s">
+      <c r="E218" s="41" t="s">
         <v>19</v>
       </c>
       <c r="F218" s="29" t="s">
@@ -6505,7 +6499,7 @@
       <c r="G218" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H218" s="49" t="s">
+      <c r="H218" s="42" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6520,7 +6514,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="38" t="s">
+      <c r="A220" s="46" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6546,7 +6540,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="38"/>
+      <c r="A221" s="46"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6576,7 +6570,7 @@
       <c r="B222" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C222" s="44" t="s">
+      <c r="C222" s="32" t="s">
         <v>35</v>
       </c>
       <c r="D222" s="24" t="s">
@@ -6781,74 +6775,74 @@
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B230" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="C230" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D230" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="E230" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="F230" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="G230" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="H230" s="41" t="s">
+      <c r="B230" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C230" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D230" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E230" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F230" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G230" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H230" s="35" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A231" s="39" t="s">
+      <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B231" s="42" t="s">
+      <c r="B231" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C231" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D231" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="E231" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F231" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="G231" s="40" t="s">
+      <c r="C231" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D231" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F231" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="H231" s="41" t="s">
+      <c r="H231" s="35" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A232" s="50" t="s">
+      <c r="A232" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B232" s="45" t="s">
+      <c r="B232" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C232" s="45" t="s">
+      <c r="C232" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="D232" s="45" t="s">
+      <c r="D232" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="E232" s="45" t="s">
+      <c r="E232" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="F232" s="51" t="s">
+      <c r="F232" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="G232" s="52" t="s">
+      <c r="G232" s="45" t="s">
         <v>10</v>
       </c>
       <c r="H232" s="29" t="s">
@@ -6877,12 +6871,17 @@
       <c r="G233" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="H233" s="47" t="s">
+      <c r="H233" s="40" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
@@ -6895,11 +6894,6 @@
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6908,26 +6902,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -7128,10 +7102,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7148,20 +7153,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C241B4B-405A-4B29-A08D-1D78DC68F8ED}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EE363E8-00D0-4980-88C5-8893823D6BCD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -471,7 +471,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -563,6 +563,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1010,7 +1013,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1057,7 +1060,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="51"/>
+      <c r="A2" s="52"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1575,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1598,7 +1601,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="51"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1882,7 +1885,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1908,7 +1911,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="51"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2192,7 +2195,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="47" t="s">
+      <c r="A40" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2218,7 +2221,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="47"/>
+      <c r="A41" s="48"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2502,7 +2505,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="47" t="s">
+      <c r="A53" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2528,7 +2531,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="47"/>
+      <c r="A54" s="48"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2812,7 +2815,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="47" t="s">
+      <c r="A66" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2838,7 +2841,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="47"/>
+      <c r="A67" s="48"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3122,7 +3125,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="47" t="s">
+      <c r="A79" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3148,7 +3151,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="47"/>
+      <c r="A80" s="48"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3268,8 +3271,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="48"/>
-      <c r="H84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="50"/>
     </row>
     <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
@@ -3428,7 +3431,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="47" t="s">
+      <c r="A92" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3454,7 +3457,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="47"/>
+      <c r="A93" s="48"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3712,7 +3715,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="47" t="s">
+      <c r="A104" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3738,7 +3741,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="47"/>
+      <c r="A105" s="48"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3996,7 +3999,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="47" t="s">
+      <c r="A116" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4022,7 +4025,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="47"/>
+      <c r="A117" s="48"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4694,7 +4697,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="47" t="s">
+      <c r="A145" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4720,7 +4723,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="47"/>
+      <c r="A146" s="48"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5056,7 +5059,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="47" t="s">
+      <c r="A160" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5082,7 +5085,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="47"/>
+      <c r="A161" s="48"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5418,7 +5421,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="47" t="s">
+      <c r="A175" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5444,7 +5447,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="47"/>
+      <c r="A176" s="48"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5780,7 +5783,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="47" t="s">
+      <c r="A190" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5806,7 +5809,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="47"/>
+      <c r="A191" s="48"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6142,7 +6145,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="46" t="s">
+      <c r="A205" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6168,7 +6171,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="46"/>
+      <c r="A206" s="47"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6441,10 +6444,10 @@
       <c r="E216" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F216" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="G216" s="38" t="s">
+      <c r="F216" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="G216" s="39" t="s">
         <v>11</v>
       </c>
       <c r="H216" s="29" t="s">
@@ -6464,7 +6467,7 @@
       <c r="D217" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E217" s="39" t="s">
+      <c r="E217" s="40" t="s">
         <v>31</v>
       </c>
       <c r="F217" s="37" t="s">
@@ -6473,7 +6476,7 @@
       <c r="G217" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="H217" s="40" t="s">
+      <c r="H217" s="41" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6490,7 +6493,7 @@
       <c r="D218" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E218" s="41" t="s">
+      <c r="E218" s="42" t="s">
         <v>19</v>
       </c>
       <c r="F218" s="29" t="s">
@@ -6499,7 +6502,7 @@
       <c r="G218" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H218" s="42" t="s">
+      <c r="H218" s="43" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6514,7 +6517,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="46" t="s">
+      <c r="A220" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6540,7 +6543,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="46"/>
+      <c r="A221" s="47"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6570,7 +6573,7 @@
       <c r="B222" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C222" s="32" t="s">
+      <c r="C222" s="38" t="s">
         <v>35</v>
       </c>
       <c r="D222" s="24" t="s">
@@ -6824,25 +6827,25 @@
       </c>
     </row>
     <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A232" s="43" t="s">
+      <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B232" s="38" t="s">
+      <c r="B232" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C232" s="38" t="s">
+      <c r="C232" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D232" s="38" t="s">
+      <c r="D232" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E232" s="38" t="s">
+      <c r="E232" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F232" s="44" t="s">
+      <c r="F232" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G232" s="45" t="s">
+      <c r="G232" s="46" t="s">
         <v>10</v>
       </c>
       <c r="H232" s="29" t="s">
@@ -6871,7 +6874,7 @@
       <c r="G233" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="H233" s="40" t="s">
+      <c r="H233" s="41" t="s">
         <v>34</v>
       </c>
     </row>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EE363E8-00D0-4980-88C5-8893823D6BCD}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8523CC63-A23F-4D67-B0B7-88F4180EEA8F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="45">
   <si>
     <t>GESTOR</t>
   </si>
@@ -592,22 +592,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1000,20 +1000,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O233"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O248"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1059,8 +1059,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="48"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1574,8 +1574,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1600,8 +1600,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="52"/>
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="48"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1884,8 +1884,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="51" t="s">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1910,8 +1910,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="52"/>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="48"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2194,8 +2194,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="48" t="s">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2220,8 +2220,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="49"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2504,8 +2504,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="48" t="s">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2530,8 +2530,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="48"/>
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="49"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2814,8 +2814,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="48" t="s">
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2840,8 +2840,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="48"/>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="49"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3124,8 +3124,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="48" t="s">
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3150,8 +3150,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="48"/>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="49"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3271,10 +3271,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="49"/>
-      <c r="H84" s="50"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G84" s="51"/>
+      <c r="H84" s="52"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3430,8 +3430,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="48" t="s">
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3456,8 +3456,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="48"/>
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="49"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3714,8 +3714,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="48" t="s">
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3740,8 +3740,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="48"/>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="49"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -3998,8 +3998,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="48" t="s">
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4024,8 +4024,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="48"/>
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="49"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4384,7 +4384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4696,8 +4696,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" s="48" t="s">
+    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4722,8 +4722,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="48"/>
+    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A146" s="49"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5058,8 +5058,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A160" s="48" t="s">
+    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5084,8 +5084,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="48"/>
+    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="49"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5160,7 +5160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5420,8 +5420,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="48" t="s">
+    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5446,8 +5446,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A176" s="48"/>
+    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="49"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5782,8 +5782,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A190" s="48" t="s">
+    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A190" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5808,8 +5808,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="48"/>
+    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A191" s="49"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6144,8 +6144,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="47" t="s">
+    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A205" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6170,8 +6170,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="47"/>
+    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A206" s="50"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6516,8 +6516,8 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="47" t="s">
+    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A220" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6542,8 +6542,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="47"/>
+    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A221" s="50"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -6878,13 +6878,371 @@
         <v>34</v>
       </c>
     </row>
+    <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A235" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B235" s="26">
+        <v>46251</v>
+      </c>
+      <c r="C235" s="26">
+        <v>46252</v>
+      </c>
+      <c r="D235" s="26">
+        <v>46253</v>
+      </c>
+      <c r="E235" s="26">
+        <v>46254</v>
+      </c>
+      <c r="F235" s="26">
+        <v>46255</v>
+      </c>
+      <c r="G235" s="26">
+        <v>46256</v>
+      </c>
+      <c r="H235" s="26">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A236" s="50"/>
+      <c r="B236" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C236" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D236" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E236" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F236" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G236" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H236" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A237" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B237" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C237" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D237" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F237" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G237" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H237" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A238" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B238" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C238" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D238" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F238" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G238" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H238" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A239" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B239" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C239" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D239" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F239" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G239" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H239" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A240" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B240" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C240" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D240" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E240" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F240" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G240" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H240" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A241" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B241" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C241" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D241" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F241" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G241" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H241" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A242" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B242" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C242" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D242" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F242" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G242" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H242" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A243" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B243" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C243" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D243" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F243" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G243" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H243" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A244" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B244" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D244" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E244" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F244" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H244" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A245" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B245" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C245" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D245" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E245" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F245" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G245" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H245" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A246" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B246" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C246" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D246" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E246" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F246" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G246" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H246" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A247" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B247" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C247" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="D247" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="E247" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="F247" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G247" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H247" s="41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A248" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B248" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C248" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D248" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E248" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F248" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G248" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H248" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+  <mergeCells count="18">
+    <mergeCell ref="A235:A236"/>
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
@@ -6897,6 +7255,11 @@
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6905,6 +7268,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -7105,27 +7488,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7142,23 +7524,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="14" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8523CC63-A23F-4D67-B0B7-88F4180EEA8F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="28680" yWindow="5280" windowWidth="23280" windowHeight="12480" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -592,22 +592,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1013,7 +1013,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1060,7 +1060,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="48"/>
+      <c r="A2" s="52"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1575,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1601,7 +1601,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="48"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1885,7 +1885,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1911,7 +1911,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="48"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2195,7 +2195,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="49" t="s">
+      <c r="A40" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2221,7 +2221,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="49"/>
+      <c r="A41" s="48"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2505,7 +2505,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="49" t="s">
+      <c r="A53" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="49"/>
+      <c r="A54" s="48"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2815,7 +2815,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="49" t="s">
+      <c r="A66" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2841,7 +2841,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="49"/>
+      <c r="A67" s="48"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3125,7 +3125,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="49" t="s">
+      <c r="A79" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3151,7 +3151,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="49"/>
+      <c r="A80" s="48"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3271,8 +3271,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="51"/>
-      <c r="H84" s="52"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="50"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
@@ -3431,7 +3431,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="49" t="s">
+      <c r="A92" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3457,7 +3457,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="49"/>
+      <c r="A93" s="48"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3715,7 +3715,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="49" t="s">
+      <c r="A104" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3741,7 +3741,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="49"/>
+      <c r="A105" s="48"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3999,7 +3999,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="49" t="s">
+      <c r="A116" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4025,7 +4025,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="49"/>
+      <c r="A117" s="48"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4697,7 +4697,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="49" t="s">
+      <c r="A145" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4723,7 +4723,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="49"/>
+      <c r="A146" s="48"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5059,7 +5059,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="49" t="s">
+      <c r="A160" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5085,7 +5085,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="49"/>
+      <c r="A161" s="48"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5421,7 +5421,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="49" t="s">
+      <c r="A175" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5447,7 +5447,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="49"/>
+      <c r="A176" s="48"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5783,7 +5783,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="49" t="s">
+      <c r="A190" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="49"/>
+      <c r="A191" s="48"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6145,7 +6145,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="50" t="s">
+      <c r="A205" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6171,7 +6171,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="50"/>
+      <c r="A206" s="47"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6517,7 +6517,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="50" t="s">
+      <c r="A220" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6543,7 +6543,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="50"/>
+      <c r="A221" s="47"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6879,7 +6879,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="50" t="s">
+      <c r="A235" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6905,7 +6905,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="50"/>
+      <c r="A236" s="47"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7242,24 +7242,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
     <mergeCell ref="A235:A236"/>
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="G84:H84"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7268,26 +7268,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -7488,10 +7468,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7508,20 +7519,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8523CC63-A23F-4D67-B0B7-88F4180EEA8F}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{951B51AD-FF0C-4423-AAA0-A9A149B6BDDE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="5280" windowWidth="23280" windowHeight="12480" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="45">
   <si>
     <t>GESTOR</t>
   </si>
@@ -471,7 +471,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -607,6 +607,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1000,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O248"/>
+  <dimension ref="A1:O263"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -7240,8 +7246,371 @@
         <v>10</v>
       </c>
     </row>
+    <row r="250" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A250" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B250" s="53">
+        <v>46258</v>
+      </c>
+      <c r="C250" s="53">
+        <v>46259</v>
+      </c>
+      <c r="D250" s="53">
+        <v>46260</v>
+      </c>
+      <c r="E250" s="53">
+        <v>46261</v>
+      </c>
+      <c r="F250" s="53">
+        <v>46262</v>
+      </c>
+      <c r="G250" s="53">
+        <v>46263</v>
+      </c>
+      <c r="H250" s="53">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A251" s="47"/>
+      <c r="B251" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C251" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D251" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="E251" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F251" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="G251" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="H251" s="54" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A252" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B252" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C252" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D252" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F252" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G252" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H252" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A253" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B253" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C253" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D253" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F253" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G253" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H253" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A254" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B254" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C254" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F254" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G254" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H254" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A255" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B255" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C255" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F255" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G255" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H255" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A256" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B256" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C256" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F256" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G256" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H256" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A257" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B257" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C257" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D257" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E257" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F257" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G257" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H257" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A258" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B258" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C258" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D258" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F258" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H258" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A259" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B259" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D259" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E259" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F259" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H259" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A260" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B260" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D260" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E260" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F260" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H260" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A261" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B261" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C261" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D261" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E261" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F261" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G261" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H261" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A262" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B262" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C262" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D262" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E262" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F262" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G262" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H262" s="41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A263" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B263" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C263" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D263" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E263" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F263" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G263" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="H263" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A250:A251"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A27:A28"/>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Horario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{951B51AD-FF0C-4423-AAA0-A9A149B6BDDE}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="6_{6E17BD36-3E42-42F2-8AFD-92DB165A9BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E88CD090-CB8A-4202-8470-A1E03FB27875}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
@@ -591,8 +591,20 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -602,18 +614,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1019,7 +1019,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1066,7 +1066,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="52"/>
+      <c r="A2" s="51"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1581,7 +1581,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1607,7 +1607,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1891,7 +1891,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="51" t="s">
+      <c r="A27" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1917,7 +1917,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2201,7 +2201,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2227,7 +2227,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="48"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2511,7 +2511,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="48" t="s">
+      <c r="A53" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2537,7 +2537,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="48"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2821,7 +2821,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="48" t="s">
+      <c r="A66" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2847,7 +2847,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="48"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="48" t="s">
+      <c r="A79" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3157,7 +3157,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="48"/>
+      <c r="A80" s="52"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3277,8 +3277,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="49"/>
-      <c r="H84" s="50"/>
+      <c r="G84" s="53"/>
+      <c r="H84" s="54"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
@@ -3437,7 +3437,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="48" t="s">
+      <c r="A92" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3463,7 +3463,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="48"/>
+      <c r="A93" s="52"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3721,7 +3721,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="48" t="s">
+      <c r="A104" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3747,7 +3747,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="48"/>
+      <c r="A105" s="52"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4005,7 +4005,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="48" t="s">
+      <c r="A116" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4031,7 +4031,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="48"/>
+      <c r="A117" s="52"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4703,7 +4703,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="48" t="s">
+      <c r="A145" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4729,7 +4729,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="48"/>
+      <c r="A146" s="52"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5065,7 +5065,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="48" t="s">
+      <c r="A160" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5091,7 +5091,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="48"/>
+      <c r="A161" s="52"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5427,7 +5427,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="48" t="s">
+      <c r="A175" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5453,7 +5453,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="48"/>
+      <c r="A176" s="52"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5789,7 +5789,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="48" t="s">
+      <c r="A190" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5815,7 +5815,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="48"/>
+      <c r="A191" s="52"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6151,7 +6151,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="47" t="s">
+      <c r="A205" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6177,7 +6177,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="47"/>
+      <c r="A206" s="49"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6523,7 +6523,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="47" t="s">
+      <c r="A220" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6549,7 +6549,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="47"/>
+      <c r="A221" s="49"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6885,7 +6885,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="47" t="s">
+      <c r="A235" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6911,7 +6911,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="47"/>
+      <c r="A236" s="49"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7083,11 +7083,11 @@
       <c r="F242" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="G242" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H242" s="24" t="s">
-        <v>11</v>
+      <c r="G242" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H242" s="29" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7187,11 +7187,11 @@
       <c r="F246" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G246" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H246" s="29" t="s">
-        <v>10</v>
+      <c r="G246" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H246" s="24" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7233,66 +7233,66 @@
       <c r="D248" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E248" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F248" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="G248" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H248" s="29" t="s">
-        <v>10</v>
+      <c r="E248" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F248" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G248" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="H248" s="28" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" s="47" t="s">
+      <c r="A250" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B250" s="53">
+      <c r="B250" s="47">
         <v>46258</v>
       </c>
-      <c r="C250" s="53">
+      <c r="C250" s="47">
         <v>46259</v>
       </c>
-      <c r="D250" s="53">
+      <c r="D250" s="47">
         <v>46260</v>
       </c>
-      <c r="E250" s="53">
+      <c r="E250" s="47">
         <v>46261</v>
       </c>
-      <c r="F250" s="53">
+      <c r="F250" s="47">
         <v>46262</v>
       </c>
-      <c r="G250" s="53">
+      <c r="G250" s="47">
         <v>46263</v>
       </c>
-      <c r="H250" s="53">
+      <c r="H250" s="47">
         <v>46264</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A251" s="47"/>
-      <c r="B251" s="54" t="s">
+      <c r="A251" s="49"/>
+      <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C251" s="54" t="s">
+      <c r="C251" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D251" s="54" t="s">
+      <c r="D251" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E251" s="54" t="s">
+      <c r="E251" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="F251" s="54" t="s">
+      <c r="F251" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="G251" s="54" t="s">
+      <c r="G251" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H251" s="54" t="s">
+      <c r="H251" s="48" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7610,6 +7610,10 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A145:A146"/>
     <mergeCell ref="A250:A251"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
@@ -7625,10 +7629,6 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A145:A146"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7637,6 +7637,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -7837,27 +7857,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7874,23 +7893,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4C914B-7D36-4137-A739-CD8E50E073E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54E31FDE-52AD-4424-8D5B-BB2E9A9DF1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-26595" yWindow="4140" windowWidth="21600" windowHeight="11685" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -178,6 +178,9 @@
   <si>
     <t>3:00 pm - 5:00 pm / 9:00 pm - 2:00 am</t>
   </si>
+  <si>
+    <t>31-Aug</t>
+  </si>
 </sst>
 </file>
 
@@ -306,7 +309,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,6 +380,18 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE49EDD"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -474,7 +489,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -600,24 +615,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -635,6 +632,42 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1027,20 +1060,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O263"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O278"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1086,8 +1119,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="54"/>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="66"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1131,7 +1164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1178,7 +1211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1225,7 +1258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1272,7 +1305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1319,7 +1352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1366,7 +1399,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1413,7 +1446,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1460,7 +1493,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1507,7 +1540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1554,7 +1587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1601,8 +1634,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="53" t="s">
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1627,8 +1660,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="54"/>
+    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="66"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1651,7 +1684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1677,7 +1710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1703,7 +1736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1729,7 +1762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1755,7 +1788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1781,7 +1814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1807,7 +1840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1833,7 +1866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1859,7 +1892,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1885,7 +1918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1911,8 +1944,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="53" t="s">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1937,8 +1970,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="54"/>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="66"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1961,7 +1994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1987,7 +2020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2013,7 +2046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2039,7 +2072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2065,7 +2098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2091,7 +2124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2117,7 +2150,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2143,7 +2176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2169,7 +2202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2195,7 +2228,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2221,8 +2254,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="51" t="s">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2247,8 +2280,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="51"/>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="64"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2271,7 +2304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2297,7 +2330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2323,7 +2356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2349,7 +2382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2375,7 +2408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2401,7 +2434,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2427,7 +2460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2453,7 +2486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2479,7 +2512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2505,7 +2538,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2531,8 +2564,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="51" t="s">
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2557,8 +2590,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="51"/>
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="64"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2581,7 +2614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2607,7 +2640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2633,7 +2666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2659,7 +2692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2685,7 +2718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2711,7 +2744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2737,7 +2770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2763,7 +2796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2789,7 +2822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2815,7 +2848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2841,8 +2874,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="51" t="s">
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2867,8 +2900,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="51"/>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="64"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2891,7 +2924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2917,7 +2950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2943,7 +2976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2969,7 +3002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -2995,7 +3028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3021,7 +3054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3047,7 +3080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3073,7 +3106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3099,7 +3132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3125,7 +3158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3151,8 +3184,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="51" t="s">
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3177,8 +3210,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="51"/>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="64"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3201,7 +3234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3227,7 +3260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3253,7 +3286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3279,7 +3312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3298,10 +3331,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="49"/>
-      <c r="H84" s="50"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G84" s="62"/>
+      <c r="H84" s="63"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3327,7 +3360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3353,7 +3386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3379,7 +3412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3405,7 +3438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3431,7 +3464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3457,8 +3490,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="51" t="s">
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3483,8 +3516,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="51"/>
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="64"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3507,7 +3540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3533,7 +3566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3559,7 +3592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3585,7 +3618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3611,7 +3644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3637,7 +3670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3663,7 +3696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3689,7 +3722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3715,7 +3748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3741,8 +3774,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A104" s="51" t="s">
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3767,8 +3800,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A105" s="51"/>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="64"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3791,7 +3824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3817,7 +3850,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3843,7 +3876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3869,7 +3902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3895,7 +3928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3921,7 +3954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3947,7 +3980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3973,7 +4006,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -3999,7 +4032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4025,8 +4058,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="51" t="s">
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4051,8 +4084,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="51"/>
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="64"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4075,7 +4108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4101,7 +4134,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4127,7 +4160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4153,7 +4186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4179,7 +4212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4205,7 +4238,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4231,7 +4264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4257,7 +4290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4283,7 +4316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4309,7 +4342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4335,7 +4368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4361,7 +4394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4387,7 +4420,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4411,7 +4444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4437,7 +4470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4463,7 +4496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4489,7 +4522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4515,7 +4548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4541,7 +4574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4567,7 +4600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4593,7 +4626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4619,7 +4652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4645,7 +4678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4671,7 +4704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4697,7 +4730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4723,8 +4756,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="51" t="s">
+    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4749,8 +4782,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="51"/>
+    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A146" s="64"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4773,7 +4806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4799,7 +4832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4825,7 +4858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4851,7 +4884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4877,7 +4910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4903,7 +4936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4929,7 +4962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4955,7 +4988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4981,7 +5014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5007,7 +5040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5033,7 +5066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5059,7 +5092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5085,8 +5118,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A160" s="51" t="s">
+    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5111,8 +5144,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A161" s="51"/>
+    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="64"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5135,7 +5168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5161,7 +5194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5187,7 +5220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5213,7 +5246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5239,7 +5272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5265,7 +5298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5291,7 +5324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5317,7 +5350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5343,7 +5376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5369,7 +5402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5395,7 +5428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5421,7 +5454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5447,8 +5480,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A175" s="51" t="s">
+    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5473,8 +5506,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A176" s="51"/>
+    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="64"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5497,7 +5530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5523,7 +5556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5549,7 +5582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5575,7 +5608,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5601,7 +5634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5627,7 +5660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5653,7 +5686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5679,7 +5712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5705,7 +5738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5731,7 +5764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5757,7 +5790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5783,7 +5816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5809,8 +5842,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A190" s="51" t="s">
+    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A190" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5835,8 +5868,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A191" s="51"/>
+    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A191" s="64"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5859,7 +5892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5885,7 +5918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5911,7 +5944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5937,7 +5970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -5963,7 +5996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -5989,7 +6022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -6015,7 +6048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6041,7 +6074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6067,7 +6100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6093,7 +6126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6119,7 +6152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6145,7 +6178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6171,8 +6204,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A205" s="52" t="s">
+    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A205" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6197,8 +6230,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A206" s="52"/>
+    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A206" s="60"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6221,7 +6254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6247,7 +6280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6273,7 +6306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6299,7 +6332,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6325,7 +6358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6351,7 +6384,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6377,7 +6410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6403,7 +6436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6429,7 +6462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6455,7 +6488,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6481,7 +6514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6507,7 +6540,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6533,7 +6566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6543,8 +6576,8 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A220" s="52" t="s">
+    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A220" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6569,8 +6602,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A221" s="52"/>
+    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A221" s="60"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6593,7 +6626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6619,7 +6652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6645,7 +6678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6671,7 +6704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6697,7 +6730,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6723,7 +6756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6749,7 +6782,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6775,7 +6808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -6801,7 +6834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6827,7 +6860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6853,7 +6886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -6879,7 +6912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -6905,8 +6938,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A235" s="52" t="s">
+    <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A235" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6931,8 +6964,8 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A236" s="52"/>
+    <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A236" s="60"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -6955,7 +6988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -6981,7 +7014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7007,7 +7040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7033,7 +7066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7059,7 +7092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7085,7 +7118,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7111,7 +7144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7137,7 +7170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7163,7 +7196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7189,7 +7222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7215,7 +7248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7241,7 +7274,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7267,8 +7300,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A250" s="52" t="s">
+    <row r="250" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A250" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7293,8 +7326,8 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A251" s="52"/>
+    <row r="251" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A251" s="60"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7317,320 +7350,682 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B252" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C252" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D252" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E252" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F252" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G252" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="H252" s="56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B252" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C252" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D252" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F252" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G252" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="H252" s="50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B253" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C253" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D253" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E253" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F253" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G253" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H253" s="55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B253" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C253" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D253" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F253" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G253" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H253" s="49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B254" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C254" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D254" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E254" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F254" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G254" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H254" s="55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B254" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C254" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F254" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G254" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H254" s="49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B255" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C255" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D255" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E255" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F255" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G255" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H255" s="55" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B255" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C255" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F255" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G255" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H255" s="49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B256" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C256" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D256" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E256" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F256" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G256" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="H256" s="56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B256" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C256" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F256" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G256" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H256" s="50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B257" s="55" t="s">
+      <c r="B257" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="C257" s="55" t="s">
+      <c r="C257" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="D257" s="55" t="s">
+      <c r="D257" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E257" s="55" t="s">
+      <c r="E257" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="F257" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G257" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H257" s="55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F257" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G257" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H257" s="49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B258" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C258" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D258" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E258" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F258" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G258" s="55" t="s">
+      <c r="B258" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C258" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D258" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F258" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H258" s="56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="H258" s="50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B259" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C259" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D259" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E259" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F259" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G259" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H259" s="56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B259" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D259" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E259" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F259" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="H259" s="50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B260" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C260" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D260" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E260" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F260" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G260" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H260" s="55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B260" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D260" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E260" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F260" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H260" s="49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B261" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="C261" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D261" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="E261" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="F261" s="55" t="s">
+      <c r="B261" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C261" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D261" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E261" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F261" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="G261" s="57" t="s">
+      <c r="G261" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H261" s="57" t="s">
+      <c r="H261" s="51" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B262" s="55" t="s">
+      <c r="B262" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="C262" s="55" t="s">
+      <c r="C262" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="D262" s="55" t="s">
+      <c r="D262" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="E262" s="55" t="s">
+      <c r="E262" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="F262" s="55" t="s">
+      <c r="F262" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="G262" s="58" t="s">
+      <c r="G262" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="H262" s="59" t="s">
+      <c r="H262" s="53" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B263" s="60" t="s">
+      <c r="B263" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="C263" s="60" t="s">
+      <c r="C263" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="D263" s="60" t="s">
+      <c r="D263" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="E263" s="60" t="s">
+      <c r="E263" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="F263" s="60" t="s">
+      <c r="F263" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="G263" s="60" t="s">
+      <c r="G263" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="H263" s="60" t="s">
+      <c r="H263" s="54" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="265" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A265" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B265" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C265" s="47">
+        <v>46266</v>
+      </c>
+      <c r="D265" s="47">
+        <v>46267</v>
+      </c>
+      <c r="E265" s="47">
+        <v>46268</v>
+      </c>
+      <c r="F265" s="47">
+        <v>46269</v>
+      </c>
+      <c r="G265" s="47">
+        <v>46270</v>
+      </c>
+      <c r="H265" s="47">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A266" s="61"/>
+      <c r="B266" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C266" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D266" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E266" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F266" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G266" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H266" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A267" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B267" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C267" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D267" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E267" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F267" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G267" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H267" s="55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A268" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B268" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C268" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D268" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F268" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G268" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="H268" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A269" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B269" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C269" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D269" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E269" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F269" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G269" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H269" s="55" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A270" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B270" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C270" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E270" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F270" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G270" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H270" s="55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A271" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B271" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C271" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D271" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E271" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F271" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G271" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H271" s="55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A272" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B272" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C272" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="D272" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="E272" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F272" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G272" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H272" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A273" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B273" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D273" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E273" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F273" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="H273" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A274" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B274" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D274" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E274" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F274" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H274" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A275" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B275" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C275" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D275" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E275" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F275" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="G275" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H275" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A276" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B276" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C276" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D276" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E276" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F276" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G276" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H276" s="55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A277" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B277" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C277" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D277" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E277" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F277" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G277" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H277" s="58" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A278" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B278" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="C278" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="D278" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="E278" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="F278" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="G278" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="H278" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="A116:A117"/>
     <mergeCell ref="A104:A105"/>
@@ -7641,6 +8036,7 @@
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A265:A266"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54E31FDE-52AD-4424-8D5B-BB2E9A9DF1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9413EAD-94A7-4565-BCBB-FC4567051053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26595" yWindow="4140" windowWidth="21600" windowHeight="11685" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="20" yWindow="260" windowWidth="19180" windowHeight="11260" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -309,7 +309,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,18 +380,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE49EDD"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -489,7 +477,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -639,13 +627,13 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -659,15 +647,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -703,7 +682,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>195</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:rowOff>109855</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1073,7 +1052,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1120,7 +1099,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
+      <c r="A2" s="59"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1635,7 +1614,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1661,7 +1640,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="66"/>
+      <c r="A15" s="59"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1945,7 +1924,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1971,7 +1950,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="66"/>
+      <c r="A28" s="59"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2255,7 +2234,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2281,7 +2260,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="64"/>
+      <c r="A41" s="57"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2565,7 +2544,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="64" t="s">
+      <c r="A53" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2591,7 +2570,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="64"/>
+      <c r="A54" s="57"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2875,7 +2854,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="64" t="s">
+      <c r="A66" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2901,7 +2880,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="64"/>
+      <c r="A67" s="57"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3185,7 +3164,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="64" t="s">
+      <c r="A79" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3211,7 +3190,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="64"/>
+      <c r="A80" s="57"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3491,7 +3470,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="64" t="s">
+      <c r="A92" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3517,7 +3496,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="64"/>
+      <c r="A93" s="57"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3775,7 +3754,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="64" t="s">
+      <c r="A104" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3801,7 +3780,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="64"/>
+      <c r="A105" s="57"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4059,7 +4038,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="64" t="s">
+      <c r="A116" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4085,7 +4064,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="64"/>
+      <c r="A117" s="57"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4757,7 +4736,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="64" t="s">
+      <c r="A145" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4783,7 +4762,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="64"/>
+      <c r="A146" s="57"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5119,7 +5098,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="64" t="s">
+      <c r="A160" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5145,7 +5124,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="64"/>
+      <c r="A161" s="57"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5481,7 +5460,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="64" t="s">
+      <c r="A175" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5507,7 +5486,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="64"/>
+      <c r="A176" s="57"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5843,7 +5822,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="64" t="s">
+      <c r="A190" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5869,7 +5848,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="64"/>
+      <c r="A191" s="57"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -7977,65 +7956,55 @@
         <v>27</v>
       </c>
       <c r="B277" s="55" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C277" s="55" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D277" s="55" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E277" s="55" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F277" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G277" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="H277" s="58" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="G277" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H277" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B278" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="C278" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="D278" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="E278" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="F278" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="G278" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="H278" s="29" t="s">
-        <v>10</v>
+      <c r="B278" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C278" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D278" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E278" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F278" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="G278" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="H278" s="53" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A265:A266"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
@@ -8046,6 +8015,16 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8054,6 +8033,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -8254,17 +8244,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8275,6 +8254,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8293,17 +8283,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9413EAD-94A7-4565-BCBB-FC4567051053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E01DCB1-61BA-49E3-BECC-CB24F60FE3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="260" windowWidth="19180" windowHeight="11260" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -477,7 +477,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -621,21 +621,6 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -647,6 +632,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1039,20 +1042,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O278"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O277"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1098,8 +1101,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="59"/>
+    <row r="2" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="61"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1143,7 +1146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1190,7 +1193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1237,7 +1240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1284,7 +1287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1331,7 +1334,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1378,7 +1381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1425,7 +1428,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1519,7 +1522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1566,7 +1569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1613,8 +1616,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="58" t="s">
+    <row r="14" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1639,8 +1642,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="59"/>
+    <row r="15" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="61"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1663,7 +1666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1689,7 +1692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1715,7 +1718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1741,7 +1744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1767,7 +1770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1793,7 +1796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1819,7 +1822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1845,7 +1848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1871,7 +1874,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1897,7 +1900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1923,8 +1926,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="58" t="s">
+    <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1949,8 +1952,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="59"/>
+    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="61"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1999,7 +2002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2025,7 +2028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2051,7 +2054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2103,7 +2106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2129,7 +2132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2155,7 +2158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2181,7 +2184,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2233,8 +2236,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="57" t="s">
+    <row r="40" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2259,8 +2262,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="57"/>
+    <row r="41" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="59"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2283,7 +2286,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2309,7 +2312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2335,7 +2338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2361,7 +2364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2387,7 +2390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2439,7 +2442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2465,7 +2468,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2491,7 +2494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2517,7 +2520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2543,8 +2546,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="57" t="s">
+    <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2569,8 +2572,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="57"/>
+    <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="59"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2593,7 +2596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2619,7 +2622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2645,7 +2648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2671,7 +2674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2723,7 +2726,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2749,7 +2752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2775,7 +2778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2801,7 +2804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2827,7 +2830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2853,8 +2856,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="57" t="s">
+    <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2879,8 +2882,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="57"/>
+    <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="59"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2903,7 +2906,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2955,7 +2958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2981,7 +2984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3033,7 +3036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3059,7 +3062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3085,7 +3088,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3111,7 +3114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3137,7 +3140,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3163,8 +3166,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="57" t="s">
+    <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3189,8 +3192,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="57"/>
+    <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="59"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3213,7 +3216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3239,7 +3242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3265,7 +3268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3291,7 +3294,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3310,10 +3313,10 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="62"/>
-      <c r="H84" s="63"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G84" s="57"/>
+      <c r="H84" s="58"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3339,7 +3342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3365,7 +3368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3391,7 +3394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3417,7 +3420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3443,7 +3446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3469,8 +3472,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="57" t="s">
+    <row r="92" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3495,8 +3498,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="57"/>
+    <row r="93" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="59"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3519,7 +3522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3545,7 +3548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3571,7 +3574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3597,7 +3600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3623,7 +3626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3649,7 +3652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3675,7 +3678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3701,7 +3704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3727,7 +3730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3753,8 +3756,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="57" t="s">
+    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A104" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3779,8 +3782,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="57"/>
+    <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="59"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3803,7 +3806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3829,7 +3832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3855,7 +3858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3881,7 +3884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3907,7 +3910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3933,7 +3936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3959,7 +3962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3985,7 +3988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -4011,7 +4014,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4037,8 +4040,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="57" t="s">
+    <row r="116" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A116" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4063,8 +4066,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="57"/>
+    <row r="117" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A117" s="59"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4087,7 +4090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4113,7 +4116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4139,7 +4142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4165,7 +4168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4191,7 +4194,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4217,7 +4220,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4243,7 +4246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4269,7 +4272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4295,7 +4298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4321,7 +4324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4347,7 +4350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4373,7 +4376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4399,7 +4402,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4423,7 +4426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4449,7 +4452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4475,7 +4478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4501,7 +4504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4527,7 +4530,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4553,7 +4556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4579,7 +4582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4605,7 +4608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4631,7 +4634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4657,7 +4660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4683,7 +4686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4709,7 +4712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4735,8 +4738,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="57" t="s">
+    <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A145" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4761,8 +4764,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="57"/>
+    <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A146" s="59"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4785,7 +4788,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4811,7 +4814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4837,7 +4840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4863,7 +4866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4889,7 +4892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4915,7 +4918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4941,7 +4944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4967,7 +4970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -4993,7 +4996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5019,7 +5022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5045,7 +5048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5071,7 +5074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5097,8 +5100,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="57" t="s">
+    <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A160" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5123,8 +5126,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="57"/>
+    <row r="161" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A161" s="59"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5147,7 +5150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5173,7 +5176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5199,7 +5202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5225,7 +5228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5251,7 +5254,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5277,7 +5280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5303,7 +5306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5329,7 +5332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5355,7 +5358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5381,7 +5384,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5407,7 +5410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5433,7 +5436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5459,8 +5462,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="57" t="s">
+    <row r="175" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A175" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5485,8 +5488,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="57"/>
+    <row r="176" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A176" s="59"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5509,7 +5512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5535,7 +5538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5561,7 +5564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5587,7 +5590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5613,7 +5616,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5639,7 +5642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5665,7 +5668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5691,7 +5694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5717,7 +5720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5743,7 +5746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5769,7 +5772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5795,7 +5798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5821,8 +5824,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="57" t="s">
+    <row r="190" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A190" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5847,8 +5850,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="57"/>
+    <row r="191" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A191" s="59"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5871,7 +5874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5897,7 +5900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5923,7 +5926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5949,7 +5952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -5975,7 +5978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -6001,7 +6004,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -6027,7 +6030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6053,7 +6056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6079,7 +6082,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6131,7 +6134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6157,7 +6160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6183,8 +6186,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="60" t="s">
+    <row r="205" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A205" s="55" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6209,8 +6212,8 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="60"/>
+    <row r="206" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A206" s="55"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6233,7 +6236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6259,7 +6262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6285,7 +6288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6311,7 +6314,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6337,7 +6340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6363,7 +6366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6389,7 +6392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6415,7 +6418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6441,7 +6444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6493,7 +6496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6519,7 +6522,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6545,7 +6548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6555,8 +6558,8 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="60" t="s">
+    <row r="220" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A220" s="55" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6581,8 +6584,8 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="60"/>
+    <row r="221" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A221" s="55"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6605,7 +6608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6631,7 +6634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6657,7 +6660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6683,7 +6686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6709,7 +6712,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6735,7 +6738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6761,7 +6764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6787,7 +6790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -6813,7 +6816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6839,7 +6842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6865,7 +6868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -6891,7 +6894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -6917,8 +6920,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="60" t="s">
+    <row r="235" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A235" s="55" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6943,8 +6946,8 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="60"/>
+    <row r="236" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A236" s="55"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -6967,7 +6970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -6993,7 +6996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7019,7 +7022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7045,7 +7048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7071,7 +7074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7097,7 +7100,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7123,7 +7126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7149,7 +7152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7175,7 +7178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7201,7 +7204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7227,7 +7230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7253,7 +7256,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7279,8 +7282,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" s="60" t="s">
+    <row r="250" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A250" s="55" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7305,8 +7308,8 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A251" s="60"/>
+    <row r="251" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A251" s="55"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7329,7 +7332,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
@@ -7355,7 +7358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
@@ -7381,7 +7384,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
@@ -7407,7 +7410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
@@ -7433,7 +7436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
@@ -7459,7 +7462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
@@ -7485,7 +7488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
@@ -7511,7 +7514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
@@ -7537,7 +7540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
@@ -7563,7 +7566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
@@ -7589,7 +7592,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
@@ -7615,7 +7618,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
@@ -7641,8 +7644,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A265" s="60" t="s">
+    <row r="265" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A265" s="55" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7667,8 +7670,8 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A266" s="61"/>
+    <row r="266" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A266" s="56"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -7691,320 +7694,304 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A267" s="23" t="s">
+    <row r="267" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A267" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B267" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C267" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D267" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E267" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F267" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G267" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H267" s="55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A268" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B268" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C268" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D268" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E268" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F268" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G268" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="H268" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A269" s="23" t="s">
+      <c r="B267" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C267" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D267" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E267" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F267" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G267" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H267" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A268" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B269" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C269" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D269" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E269" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F269" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G269" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H269" s="55" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A270" s="23" t="s">
+      <c r="B268" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C268" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D268" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F268" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G268" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H268" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A269" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B270" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C270" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D270" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E270" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F270" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G270" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H270" s="55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A271" s="23" t="s">
+      <c r="B269" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C269" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D269" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E269" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F269" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G269" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H269" s="34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A270" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B271" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C271" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D271" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E271" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F271" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G271" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H271" s="55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A272" s="23" t="s">
+      <c r="B270" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C270" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E270" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F270" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G270" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H270" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A271" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B272" s="56" t="s">
+      <c r="B271" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C272" s="55" t="s">
+      <c r="C271" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="D272" s="55" t="s">
+      <c r="D271" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="E272" s="55" t="s">
+      <c r="E271" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F272" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G272" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H272" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A273" s="23" t="s">
+      <c r="F271" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G271" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H271" s="34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A272" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B273" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C273" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D273" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E273" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F273" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G273" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="H273" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A274" s="23" t="s">
+      <c r="B272" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C272" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D272" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E272" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F272" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G272" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H272" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A273" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B274" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C274" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D274" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E274" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F274" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G274" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H274" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A275" s="23" t="s">
+      <c r="B273" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D273" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E273" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F273" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H273" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A274" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B275" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="C275" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D275" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="E275" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="F275" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="G275" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="H275" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A276" s="23" t="s">
+      <c r="B274" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C274" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D274" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E274" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F274" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G274" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H274" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A275" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B276" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C276" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="D276" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E276" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F276" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G276" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H276" s="55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A277" s="44" t="s">
+      <c r="B275" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C275" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D275" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E275" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F275" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G275" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H275" s="34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A276" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="B277" s="55" t="s">
+      <c r="B276" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="C277" s="55" t="s">
+      <c r="C276" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="D277" s="55" t="s">
+      <c r="D276" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E277" s="55" t="s">
+      <c r="E276" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="F277" s="55" t="s">
+      <c r="F276" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="G277" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H277" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A278" s="23" t="s">
+      <c r="G276" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H276" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A277" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B278" s="55" t="s">
+      <c r="B277" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="C278" s="55" t="s">
+      <c r="C277" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D278" s="55" t="s">
+      <c r="D277" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E278" s="55" t="s">
+      <c r="E277" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="F278" s="55" t="s">
+      <c r="F277" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="G278" s="52" t="s">
+      <c r="G277" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="H278" s="53" t="s">
+      <c r="H277" s="64" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A265:A266"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
@@ -8015,16 +8002,6 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8033,14 +8010,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8245,21 +8220,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8284,9 +8258,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E01DCB1-61BA-49E3-BECC-CB24F60FE3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C640C88-B2CB-45F6-8144-1C67E35B0A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -477,7 +477,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -621,6 +621,24 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -633,22 +651,13 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1042,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O277"/>
+  <dimension ref="A1:O291"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
@@ -1055,7 +1064,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1102,7 +1111,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="61"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1617,7 +1626,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1643,7 +1652,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="61"/>
+      <c r="A15" s="60"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1927,7 +1936,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="59" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1953,7 +1962,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="61"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -2237,7 +2246,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2263,7 +2272,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="59"/>
+      <c r="A41" s="58"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2547,7 +2556,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="59" t="s">
+      <c r="A53" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2573,7 +2582,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="59"/>
+      <c r="A54" s="58"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2857,7 +2866,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="59" t="s">
+      <c r="A66" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2883,7 +2892,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="59"/>
+      <c r="A67" s="58"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -3167,7 +3176,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="59" t="s">
+      <c r="A79" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3193,7 +3202,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="59"/>
+      <c r="A80" s="58"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3313,8 +3322,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="57"/>
-      <c r="H84" s="58"/>
+      <c r="G84" s="63"/>
+      <c r="H84" s="64"/>
     </row>
     <row r="85" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
@@ -3473,7 +3482,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="59" t="s">
+      <c r="A92" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3499,7 +3508,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="59"/>
+      <c r="A93" s="58"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3757,7 +3766,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A104" s="59" t="s">
+      <c r="A104" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3783,7 +3792,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A105" s="59"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -4041,7 +4050,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="59" t="s">
+      <c r="A116" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4067,7 +4076,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="59"/>
+      <c r="A117" s="58"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4739,7 +4748,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="59" t="s">
+      <c r="A145" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4765,7 +4774,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="59"/>
+      <c r="A146" s="58"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -5101,7 +5110,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A160" s="59" t="s">
+      <c r="A160" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5127,7 +5136,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A161" s="59"/>
+      <c r="A161" s="58"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5463,7 +5472,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A175" s="59" t="s">
+      <c r="A175" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5489,7 +5498,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A176" s="59"/>
+      <c r="A176" s="58"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5825,7 +5834,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A190" s="59" t="s">
+      <c r="A190" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5851,7 +5860,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A191" s="59"/>
+      <c r="A191" s="58"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -6187,7 +6196,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A205" s="55" t="s">
+      <c r="A205" s="61" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6213,7 +6222,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A206" s="55"/>
+      <c r="A206" s="61"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6559,7 +6568,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A220" s="55" t="s">
+      <c r="A220" s="61" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6585,7 +6594,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A221" s="55"/>
+      <c r="A221" s="61"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6921,7 +6930,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A235" s="55" t="s">
+      <c r="A235" s="61" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6947,7 +6956,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A236" s="55"/>
+      <c r="A236" s="61"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7283,7 +7292,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A250" s="55" t="s">
+      <c r="A250" s="61" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7309,7 +7318,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A251" s="55"/>
+      <c r="A251" s="61"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7645,7 +7654,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A265" s="55" t="s">
+      <c r="A265" s="61" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7671,7 +7680,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A266" s="56"/>
+      <c r="A266" s="62"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -7929,22 +7938,22 @@
       </c>
     </row>
     <row r="276" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A276" s="62" t="s">
+      <c r="A276" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B276" s="63" t="s">
+      <c r="B276" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C276" s="63" t="s">
+      <c r="C276" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="D276" s="63" t="s">
+      <c r="D276" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="E276" s="63" t="s">
+      <c r="E276" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="F276" s="63" t="s">
+      <c r="F276" s="56" t="s">
         <v>33</v>
       </c>
       <c r="G276" s="35" t="s">
@@ -7976,22 +7985,349 @@
       <c r="G277" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="H277" s="64" t="s">
+      <c r="H277" s="57" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="279" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A279" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="66">
+        <v>46272</v>
+      </c>
+      <c r="C279" s="66">
+        <v>46273</v>
+      </c>
+      <c r="D279" s="66">
+        <v>46274</v>
+      </c>
+      <c r="E279" s="66">
+        <v>46275</v>
+      </c>
+      <c r="F279" s="66">
+        <v>46276</v>
+      </c>
+      <c r="G279" s="66">
+        <v>46277</v>
+      </c>
+      <c r="H279" s="66">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A280" s="65"/>
+      <c r="B280" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C280" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="D280" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="E280" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="F280" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="G280" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="H280" s="67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A281" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B281" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C281" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D281" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F281" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G281" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H281" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A282" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B282" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C282" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D282" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E282" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F282" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G282" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H282" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A283" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B283" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C283" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D283" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="E283" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F283" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G283" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H283" s="34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A284" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B284" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C284" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D284" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F284" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G284" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H284" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A285" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B285" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C285" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D285" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E285" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F285" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G285" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H285" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A286" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B286" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C286" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D286" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E286" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F286" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G286" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H286" s="34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A287" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B287" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C287" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D287" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E287" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F287" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G287" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H287" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A288" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B288" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C288" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D288" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E288" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F288" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H288" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A289" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B289" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C289" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D289" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E289" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F289" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G289" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H289" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A290" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B290" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C290" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D290" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E290" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F290" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G290" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H290" s="57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A291" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B291" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C291" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D291" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E291" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F291" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G291" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H291" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
+  <mergeCells count="21">
+    <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
@@ -8002,6 +8338,16 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8010,12 +8356,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8220,20 +8568,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8258,12 +8607,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C640C88-B2CB-45F6-8144-1C67E35B0A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA6AF27-50E5-48ED-A5E8-99D3689D5F08}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="47">
   <si>
     <t>GESTOR</t>
   </si>
@@ -189,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,26 +287,30 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,6 +381,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE49EDD"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -477,7 +484,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -630,14 +637,14 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -651,13 +658,22 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -694,7 +710,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>195</xdr:row>
-      <xdr:rowOff>109855</xdr:rowOff>
+      <xdr:rowOff>98425</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1051,20 +1067,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O291"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O305"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:15" ht="15.6">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -1110,8 +1126,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="60"/>
+    <row r="2" spans="1:15" ht="15.6">
+      <c r="A2" s="67"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1155,7 +1171,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="15.6">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1202,7 +1218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.6">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1249,7 +1265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="15.6">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1296,7 +1312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="15.6">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1343,7 +1359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15.6">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1390,7 +1406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.6">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1437,7 +1453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.6">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1484,7 +1500,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15.6">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1531,7 +1547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15.6">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1578,7 +1594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="15.6">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1625,8 +1641,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="59" t="s">
+    <row r="14" spans="1:15" ht="15.6">
+      <c r="A14" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1651,8 +1667,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="60"/>
+    <row r="15" spans="1:15" ht="15.6">
+      <c r="A15" s="67"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1675,7 +1691,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="15.6">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1701,7 +1717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15.6">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1727,7 +1743,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.6">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1753,7 +1769,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.6">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1779,7 +1795,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.6">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1805,7 +1821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15.6">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1831,7 +1847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15.6">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1857,7 +1873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15.6">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1883,7 +1899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15.6">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1909,7 +1925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="15.6">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1935,8 +1951,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="59" t="s">
+    <row r="27" spans="1:8" ht="15.6">
+      <c r="A27" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1961,8 +1977,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="60"/>
+    <row r="28" spans="1:8" ht="15.6">
+      <c r="A28" s="67"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1985,7 +2001,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="15.6">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -2011,7 +2027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="15.6">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -2037,7 +2053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="15.6">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -2063,7 +2079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="15.6">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2089,7 +2105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="15.6">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -2115,7 +2131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="15.6">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -2141,7 +2157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="15.6">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -2167,7 +2183,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="15.6">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -2193,7 +2209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="15.6">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -2219,7 +2235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="15.6">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -2245,8 +2261,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="58" t="s">
+    <row r="40" spans="1:8" ht="15.6">
+      <c r="A40" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -2271,8 +2287,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="58"/>
+    <row r="41" spans="1:8" ht="15.6">
+      <c r="A41" s="65"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2295,7 +2311,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="15.6">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -2321,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="15.6">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2347,7 +2363,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15.6">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2373,7 +2389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="15.6">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2399,7 +2415,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="15.6">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2425,7 +2441,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="15.6">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2451,7 +2467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="15.6">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2477,7 +2493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="15.6">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2503,7 +2519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="15.6">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2529,7 +2545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="15.6">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2555,8 +2571,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="58" t="s">
+    <row r="53" spans="1:8" ht="15.6">
+      <c r="A53" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="1">
@@ -2581,8 +2597,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="58"/>
+    <row r="54" spans="1:8" ht="15.6">
+      <c r="A54" s="65"/>
       <c r="B54" s="2" t="s">
         <v>1</v>
       </c>
@@ -2605,7 +2621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="15.6">
       <c r="A55" s="3" t="s">
         <v>22</v>
       </c>
@@ -2631,7 +2647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="15.6">
       <c r="A56" s="3" t="s">
         <v>14</v>
       </c>
@@ -2657,7 +2673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="15.6">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2683,7 +2699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="15.6">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2709,7 +2725,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="15.6">
       <c r="A59" s="3" t="s">
         <v>23</v>
       </c>
@@ -2735,7 +2751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="15.6">
       <c r="A60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2761,7 +2777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="15.6">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2787,7 +2803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="15.6">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2813,7 +2829,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="15.6">
       <c r="A63" s="3" t="s">
         <v>20</v>
       </c>
@@ -2839,7 +2855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="15.6">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -2865,8 +2881,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="58" t="s">
+    <row r="66" spans="1:8" ht="15.6">
+      <c r="A66" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="1">
@@ -2891,8 +2907,8 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="58"/>
+    <row r="67" spans="1:8" ht="15.6">
+      <c r="A67" s="65"/>
       <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
@@ -2915,7 +2931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="15.6">
       <c r="A68" s="3" t="s">
         <v>22</v>
       </c>
@@ -2941,7 +2957,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="15.6">
       <c r="A69" s="3" t="s">
         <v>21</v>
       </c>
@@ -2967,7 +2983,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="15.6">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -2993,7 +3009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="15.6">
       <c r="A71" s="3" t="s">
         <v>18</v>
       </c>
@@ -3019,7 +3035,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="15.6">
       <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
@@ -3045,7 +3061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="15.6">
       <c r="A73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3071,7 +3087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="15.6">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -3097,7 +3113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="15.6">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -3123,7 +3139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="15.6">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -3149,7 +3165,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="15.6">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -3175,8 +3191,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="58" t="s">
+    <row r="79" spans="1:8" ht="15.6">
+      <c r="A79" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="1">
@@ -3201,8 +3217,8 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="58"/>
+    <row r="80" spans="1:8" ht="15.6">
+      <c r="A80" s="65"/>
       <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
@@ -3225,7 +3241,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="15.6">
       <c r="A81" s="3" t="s">
         <v>22</v>
       </c>
@@ -3251,7 +3267,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="15.6">
       <c r="A82" s="3" t="s">
         <v>14</v>
       </c>
@@ -3277,7 +3293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="15.6">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3303,7 +3319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="15.6">
       <c r="A84" s="3" t="s">
         <v>15</v>
       </c>
@@ -3325,7 +3341,7 @@
       <c r="G84" s="63"/>
       <c r="H84" s="64"/>
     </row>
-    <row r="85" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="15.6">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3351,7 +3367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15.6">
       <c r="A86" s="3" t="s">
         <v>18</v>
       </c>
@@ -3377,7 +3393,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="15.6">
       <c r="A87" s="3" t="s">
         <v>21</v>
       </c>
@@ -3403,7 +3419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="15.6">
       <c r="A88" s="3" t="s">
         <v>8</v>
       </c>
@@ -3429,7 +3445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="15.6">
       <c r="A89" s="3" t="s">
         <v>20</v>
       </c>
@@ -3455,7 +3471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="15.6">
       <c r="A90" s="3" t="s">
         <v>23</v>
       </c>
@@ -3481,8 +3497,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="58" t="s">
+    <row r="92" spans="1:8" ht="15.6">
+      <c r="A92" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="1">
@@ -3507,8 +3523,8 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="58"/>
+    <row r="93" spans="1:8" ht="15.6">
+      <c r="A93" s="65"/>
       <c r="B93" s="2" t="s">
         <v>1</v>
       </c>
@@ -3531,7 +3547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="15.6">
       <c r="A94" s="3" t="s">
         <v>22</v>
       </c>
@@ -3557,7 +3573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="15.6">
       <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
@@ -3583,7 +3599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="15.6">
       <c r="A96" s="3" t="s">
         <v>8</v>
       </c>
@@ -3609,7 +3625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="15.6">
       <c r="A97" s="3" t="s">
         <v>23</v>
       </c>
@@ -3635,7 +3651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="15.6">
       <c r="A98" s="3" t="s">
         <v>18</v>
       </c>
@@ -3661,7 +3677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="15.6">
       <c r="A99" s="3" t="s">
         <v>14</v>
       </c>
@@ -3687,7 +3703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="15.6">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -3713,7 +3729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="15.6">
       <c r="A101" s="3" t="s">
         <v>20</v>
       </c>
@@ -3739,7 +3755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="15.6">
       <c r="A102" s="3" t="s">
         <v>17</v>
       </c>
@@ -3765,8 +3781,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A104" s="58" t="s">
+    <row r="104" spans="1:8" ht="15.6">
+      <c r="A104" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="1">
@@ -3791,8 +3807,8 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A105" s="58"/>
+    <row r="105" spans="1:8" ht="15.6">
+      <c r="A105" s="65"/>
       <c r="B105" s="2" t="s">
         <v>1</v>
       </c>
@@ -3815,7 +3831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="15.6">
       <c r="A106" s="3" t="s">
         <v>22</v>
       </c>
@@ -3841,7 +3857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="15.6">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -3867,7 +3883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="15.6">
       <c r="A108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3893,7 +3909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="15.6">
       <c r="A109" s="3" t="s">
         <v>20</v>
       </c>
@@ -3919,7 +3935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="15.6">
       <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
@@ -3945,7 +3961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="15.6">
       <c r="A111" s="3" t="s">
         <v>18</v>
       </c>
@@ -3971,7 +3987,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="15.6">
       <c r="A112" s="3" t="s">
         <v>14</v>
       </c>
@@ -3997,7 +4013,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="15.6">
       <c r="A113" s="3" t="s">
         <v>8</v>
       </c>
@@ -4023,7 +4039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="15.6">
       <c r="A114" s="3" t="s">
         <v>21</v>
       </c>
@@ -4049,8 +4065,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="58" t="s">
+    <row r="116" spans="1:8" ht="15.6">
+      <c r="A116" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="1">
@@ -4075,8 +4091,8 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="58"/>
+    <row r="117" spans="1:8" ht="15.6">
+      <c r="A117" s="65"/>
       <c r="B117" s="2" t="s">
         <v>1</v>
       </c>
@@ -4099,7 +4115,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="15.6">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -4125,7 +4141,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="15.6">
       <c r="A119" s="3" t="s">
         <v>22</v>
       </c>
@@ -4151,7 +4167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="15.6">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -4177,7 +4193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="15.6">
       <c r="A121" s="3" t="s">
         <v>23</v>
       </c>
@@ -4203,7 +4219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="15.6">
       <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
@@ -4229,7 +4245,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="15.6">
       <c r="A123" s="3" t="s">
         <v>12</v>
       </c>
@@ -4255,7 +4271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="15.6">
       <c r="A124" s="3" t="s">
         <v>17</v>
       </c>
@@ -4281,7 +4297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="15.6">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -4307,7 +4323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="15.6">
       <c r="A126" s="3" t="s">
         <v>14</v>
       </c>
@@ -4333,7 +4349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="15.6">
       <c r="A127" s="3" t="s">
         <v>27</v>
       </c>
@@ -4359,7 +4375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="15.6">
       <c r="A128" s="3" t="s">
         <v>28</v>
       </c>
@@ -4385,7 +4401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" ht="15.6">
       <c r="A130" s="11" t="s">
         <v>0</v>
       </c>
@@ -4411,7 +4427,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="15.6">
       <c r="A131" s="11"/>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -4435,7 +4451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" ht="15.6">
       <c r="A132" s="3" t="s">
         <v>22</v>
       </c>
@@ -4461,7 +4477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" ht="15.6">
       <c r="A133" s="3" t="s">
         <v>29</v>
       </c>
@@ -4487,7 +4503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" ht="15.6">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -4513,7 +4529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" ht="15.6">
       <c r="A135" s="3" t="s">
         <v>17</v>
       </c>
@@ -4539,7 +4555,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" ht="15.6">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -4565,7 +4581,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" ht="15.6">
       <c r="A137" s="3" t="s">
         <v>14</v>
       </c>
@@ -4591,7 +4607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" ht="15.6">
       <c r="A138" s="3" t="s">
         <v>18</v>
       </c>
@@ -4617,7 +4633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" ht="15.6">
       <c r="A139" s="3" t="s">
         <v>23</v>
       </c>
@@ -4643,7 +4659,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" ht="15.6">
       <c r="A140" s="3" t="s">
         <v>21</v>
       </c>
@@ -4669,7 +4685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="15.6">
       <c r="A141" s="3" t="s">
         <v>8</v>
       </c>
@@ -4695,7 +4711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="15.6">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4721,7 +4737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="15.6">
       <c r="A143" s="3" t="s">
         <v>28</v>
       </c>
@@ -4747,8 +4763,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="58" t="s">
+    <row r="145" spans="1:8" ht="15.6">
+      <c r="A145" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="1">
@@ -4773,8 +4789,8 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="58"/>
+    <row r="146" spans="1:8" ht="15.6">
+      <c r="A146" s="65"/>
       <c r="B146" s="2" t="s">
         <v>1</v>
       </c>
@@ -4797,7 +4813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="15.6">
       <c r="A147" s="3" t="s">
         <v>22</v>
       </c>
@@ -4823,7 +4839,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="15.6">
       <c r="A148" s="3" t="s">
         <v>29</v>
       </c>
@@ -4849,7 +4865,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="15.6">
       <c r="A149" s="3" t="s">
         <v>14</v>
       </c>
@@ -4875,7 +4891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="15.6">
       <c r="A150" s="3" t="s">
         <v>18</v>
       </c>
@@ -4901,7 +4917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="15.6">
       <c r="A151" s="3" t="s">
         <v>20</v>
       </c>
@@ -4927,7 +4943,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="15.6">
       <c r="A152" s="3" t="s">
         <v>21</v>
       </c>
@@ -4953,7 +4969,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="15.6">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -4979,7 +4995,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="15.6">
       <c r="A154" s="3" t="s">
         <v>8</v>
       </c>
@@ -5005,7 +5021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="15.6">
       <c r="A155" s="3" t="s">
         <v>17</v>
       </c>
@@ -5031,7 +5047,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="15.6">
       <c r="A156" s="3" t="s">
         <v>23</v>
       </c>
@@ -5057,7 +5073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="15.6">
       <c r="A157" s="3" t="s">
         <v>27</v>
       </c>
@@ -5083,7 +5099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="15.6">
       <c r="A158" s="3" t="s">
         <v>28</v>
       </c>
@@ -5109,8 +5125,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A160" s="58" t="s">
+    <row r="160" spans="1:8" ht="15.6">
+      <c r="A160" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="1">
@@ -5135,8 +5151,8 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A161" s="58"/>
+    <row r="161" spans="1:8" ht="15.6">
+      <c r="A161" s="65"/>
       <c r="B161" s="2" t="s">
         <v>1</v>
       </c>
@@ -5159,7 +5175,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="15.6">
       <c r="A162" s="3" t="s">
         <v>22</v>
       </c>
@@ -5185,7 +5201,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" ht="15.6">
       <c r="A163" s="3" t="s">
         <v>29</v>
       </c>
@@ -5211,7 +5227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="15.6">
       <c r="A164" s="3" t="s">
         <v>8</v>
       </c>
@@ -5237,7 +5253,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="15.6">
       <c r="A165" s="3" t="s">
         <v>17</v>
       </c>
@@ -5263,7 +5279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="15.6">
       <c r="A166" s="3" t="s">
         <v>21</v>
       </c>
@@ -5289,7 +5305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="15.6">
       <c r="A167" s="3" t="s">
         <v>14</v>
       </c>
@@ -5315,7 +5331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="15.6">
       <c r="A168" s="3" t="s">
         <v>23</v>
       </c>
@@ -5341,7 +5357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="15.6">
       <c r="A169" s="3" t="s">
         <v>18</v>
       </c>
@@ -5367,7 +5383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="15.6">
       <c r="A170" s="3" t="s">
         <v>20</v>
       </c>
@@ -5393,7 +5409,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" ht="15.6">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -5419,7 +5435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="15.6">
       <c r="A172" s="3" t="s">
         <v>27</v>
       </c>
@@ -5445,7 +5461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" ht="15.6">
       <c r="A173" s="3" t="s">
         <v>28</v>
       </c>
@@ -5471,8 +5487,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A175" s="58" t="s">
+    <row r="175" spans="1:8" ht="15.6">
+      <c r="A175" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="1">
@@ -5497,8 +5513,8 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A176" s="58"/>
+    <row r="176" spans="1:8" ht="15.6">
+      <c r="A176" s="65"/>
       <c r="B176" s="2" t="s">
         <v>1</v>
       </c>
@@ -5521,7 +5537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="15.6">
       <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
@@ -5547,7 +5563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" ht="15.6">
       <c r="A178" s="3" t="s">
         <v>29</v>
       </c>
@@ -5573,7 +5589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="15.6">
       <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
@@ -5599,7 +5615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="15.6">
       <c r="A180" s="3" t="s">
         <v>21</v>
       </c>
@@ -5625,7 +5641,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="15.6">
       <c r="A181" s="3" t="s">
         <v>23</v>
       </c>
@@ -5651,7 +5667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="15.6">
       <c r="A182" s="3" t="s">
         <v>18</v>
       </c>
@@ -5677,7 +5693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="15.6">
       <c r="A183" s="3" t="s">
         <v>17</v>
       </c>
@@ -5703,7 +5719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="15.6">
       <c r="A184" s="3" t="s">
         <v>14</v>
       </c>
@@ -5729,7 +5745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="15.6">
       <c r="A185" s="3" t="s">
         <v>8</v>
       </c>
@@ -5755,7 +5771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="15.6">
       <c r="A186" s="3" t="s">
         <v>20</v>
       </c>
@@ -5781,7 +5797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="15.6">
       <c r="A187" s="3" t="s">
         <v>28</v>
       </c>
@@ -5807,7 +5823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="15.6">
       <c r="A188" s="3" t="s">
         <v>27</v>
       </c>
@@ -5833,8 +5849,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A190" s="58" t="s">
+    <row r="190" spans="1:8" ht="15.6">
+      <c r="A190" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="1">
@@ -5859,8 +5875,8 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A191" s="58"/>
+    <row r="191" spans="1:8" ht="15.6">
+      <c r="A191" s="65"/>
       <c r="B191" s="2" t="s">
         <v>1</v>
       </c>
@@ -5883,7 +5899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="15.6">
       <c r="A192" s="3" t="s">
         <v>22</v>
       </c>
@@ -5909,7 +5925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="15.6">
       <c r="A193" s="16" t="s">
         <v>29</v>
       </c>
@@ -5935,7 +5951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="15.6">
       <c r="A194" s="16" t="s">
         <v>14</v>
       </c>
@@ -5961,7 +5977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="15.6">
       <c r="A195" s="16" t="s">
         <v>8</v>
       </c>
@@ -5987,7 +6003,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="15.6">
       <c r="A196" s="17" t="s">
         <v>20</v>
       </c>
@@ -6013,7 +6029,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="15.6">
       <c r="A197" s="18" t="s">
         <v>23</v>
       </c>
@@ -6039,7 +6055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="15.6">
       <c r="A198" s="17" t="s">
         <v>12</v>
       </c>
@@ -6065,7 +6081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="15.6">
       <c r="A199" s="16" t="s">
         <v>21</v>
       </c>
@@ -6091,7 +6107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="15.6">
       <c r="A200" s="16" t="s">
         <v>18</v>
       </c>
@@ -6117,7 +6133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="15.6">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6143,7 +6159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="15.6">
       <c r="A202" s="16" t="s">
         <v>27</v>
       </c>
@@ -6169,7 +6185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="15.6">
       <c r="A203" s="3" t="s">
         <v>28</v>
       </c>
@@ -6195,7 +6211,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" ht="15.6">
       <c r="A205" s="61" t="s">
         <v>0</v>
       </c>
@@ -6221,7 +6237,7 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" ht="15.6">
       <c r="A206" s="61"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
@@ -6245,7 +6261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="15.6">
       <c r="A207" s="23" t="s">
         <v>22</v>
       </c>
@@ -6271,7 +6287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" ht="15.6">
       <c r="A208" s="23" t="s">
         <v>29</v>
       </c>
@@ -6297,7 +6313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="46.8">
       <c r="A209" s="23" t="s">
         <v>18</v>
       </c>
@@ -6323,7 +6339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" ht="15.6">
       <c r="A210" s="23" t="s">
         <v>20</v>
       </c>
@@ -6349,7 +6365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" ht="31.2">
       <c r="A211" s="23" t="s">
         <v>17</v>
       </c>
@@ -6375,7 +6391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="31.2">
       <c r="A212" s="23" t="s">
         <v>12</v>
       </c>
@@ -6401,7 +6417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" ht="15.6">
       <c r="A213" s="23" t="s">
         <v>14</v>
       </c>
@@ -6427,7 +6443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" ht="15.6">
       <c r="A214" s="23" t="s">
         <v>8</v>
       </c>
@@ -6453,7 +6469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="15.6">
       <c r="A215" s="23" t="s">
         <v>23</v>
       </c>
@@ -6479,7 +6495,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" ht="15.6">
       <c r="A216" s="23" t="s">
         <v>21</v>
       </c>
@@ -6505,7 +6521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" ht="15.6">
       <c r="A217" s="27" t="s">
         <v>27</v>
       </c>
@@ -6531,7 +6547,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" ht="15.6">
       <c r="A218" s="23" t="s">
         <v>28</v>
       </c>
@@ -6557,7 +6573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8">
       <c r="A219" s="22"/>
       <c r="B219" s="22"/>
       <c r="C219" s="22"/>
@@ -6567,7 +6583,7 @@
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
     </row>
-    <row r="220" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" ht="15.6">
       <c r="A220" s="61" t="s">
         <v>0</v>
       </c>
@@ -6593,7 +6609,7 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" ht="15.6">
       <c r="A221" s="61"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
@@ -6617,7 +6633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" ht="15.6">
       <c r="A222" s="23" t="s">
         <v>22</v>
       </c>
@@ -6643,7 +6659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" ht="15.6">
       <c r="A223" s="23" t="s">
         <v>29</v>
       </c>
@@ -6669,7 +6685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" ht="15.6">
       <c r="A224" s="23" t="s">
         <v>21</v>
       </c>
@@ -6695,7 +6711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" ht="15.6">
       <c r="A225" s="23" t="s">
         <v>23</v>
       </c>
@@ -6721,7 +6737,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" ht="31.2">
       <c r="A226" s="23" t="s">
         <v>17</v>
       </c>
@@ -6747,7 +6763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" ht="15.6">
       <c r="A227" s="23" t="s">
         <v>12</v>
       </c>
@@ -6773,7 +6789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="15.6">
       <c r="A228" s="23" t="s">
         <v>8</v>
       </c>
@@ -6799,7 +6815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" ht="15.6">
       <c r="A229" s="23" t="s">
         <v>20</v>
       </c>
@@ -6825,7 +6841,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" ht="15.6">
       <c r="A230" s="23" t="s">
         <v>14</v>
       </c>
@@ -6851,7 +6867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" ht="15.6">
       <c r="A231" s="33" t="s">
         <v>18</v>
       </c>
@@ -6877,7 +6893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" ht="15.6">
       <c r="A232" s="44" t="s">
         <v>27</v>
       </c>
@@ -6903,7 +6919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" ht="15.6">
       <c r="A233" s="23" t="s">
         <v>28</v>
       </c>
@@ -6929,7 +6945,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" ht="15.6">
       <c r="A235" s="61" t="s">
         <v>0</v>
       </c>
@@ -6955,7 +6971,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" ht="15.6">
       <c r="A236" s="61"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
@@ -6979,7 +6995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" ht="15.6">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -7005,7 +7021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" ht="15.6">
       <c r="A238" s="23" t="s">
         <v>29</v>
       </c>
@@ -7031,7 +7047,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" ht="15.6">
       <c r="A239" s="23" t="s">
         <v>18</v>
       </c>
@@ -7057,7 +7073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" ht="31.2">
       <c r="A240" s="23" t="s">
         <v>17</v>
       </c>
@@ -7083,7 +7099,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" ht="15.6">
       <c r="A241" s="23" t="s">
         <v>23</v>
       </c>
@@ -7109,7 +7125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" ht="15.6">
       <c r="A242" s="23" t="s">
         <v>14</v>
       </c>
@@ -7135,7 +7151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" ht="15.6">
       <c r="A243" s="23" t="s">
         <v>8</v>
       </c>
@@ -7161,7 +7177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" ht="15.6">
       <c r="A244" s="23" t="s">
         <v>21</v>
       </c>
@@ -7187,7 +7203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" ht="15.6">
       <c r="A245" s="23" t="s">
         <v>20</v>
       </c>
@@ -7213,7 +7229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" ht="15.6">
       <c r="A246" s="23" t="s">
         <v>12</v>
       </c>
@@ -7239,7 +7255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" ht="15.6">
       <c r="A247" s="44" t="s">
         <v>27</v>
       </c>
@@ -7265,7 +7281,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" ht="15.6">
       <c r="A248" s="23" t="s">
         <v>28</v>
       </c>
@@ -7291,7 +7307,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" ht="15.6">
       <c r="A250" s="61" t="s">
         <v>0</v>
       </c>
@@ -7317,7 +7333,7 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" ht="15.6">
       <c r="A251" s="61"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
@@ -7341,7 +7357,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" ht="15.6">
       <c r="A252" s="23" t="s">
         <v>22</v>
       </c>
@@ -7367,7 +7383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:8" ht="15.6">
       <c r="A253" s="23" t="s">
         <v>29</v>
       </c>
@@ -7393,7 +7409,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" ht="15.6">
       <c r="A254" s="23" t="s">
         <v>21</v>
       </c>
@@ -7419,7 +7435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" ht="15.6">
       <c r="A255" s="23" t="s">
         <v>20</v>
       </c>
@@ -7445,7 +7461,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" ht="15.6">
       <c r="A256" s="23" t="s">
         <v>23</v>
       </c>
@@ -7471,7 +7487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" ht="15.6">
       <c r="A257" s="23" t="s">
         <v>12</v>
       </c>
@@ -7497,7 +7513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" ht="15.6">
       <c r="A258" s="23" t="s">
         <v>18</v>
       </c>
@@ -7523,7 +7539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" ht="15.6">
       <c r="A259" s="23" t="s">
         <v>14</v>
       </c>
@@ -7549,7 +7565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" ht="15.6">
       <c r="A260" s="23" t="s">
         <v>8</v>
       </c>
@@ -7575,7 +7591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" ht="15.6">
       <c r="A261" s="23" t="s">
         <v>17</v>
       </c>
@@ -7601,7 +7617,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" ht="15.6">
       <c r="A262" s="44" t="s">
         <v>27</v>
       </c>
@@ -7627,7 +7643,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" ht="15.6">
       <c r="A263" s="23" t="s">
         <v>28</v>
       </c>
@@ -7653,7 +7669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" ht="15.6">
       <c r="A265" s="61" t="s">
         <v>0</v>
       </c>
@@ -7679,7 +7695,7 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" ht="15.6">
       <c r="A266" s="62"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
@@ -7703,7 +7719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" ht="15.6">
       <c r="A267" s="33" t="s">
         <v>22</v>
       </c>
@@ -7729,7 +7745,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" ht="15.6">
       <c r="A268" s="33" t="s">
         <v>8</v>
       </c>
@@ -7755,7 +7771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" ht="15.6">
       <c r="A269" s="33" t="s">
         <v>14</v>
       </c>
@@ -7781,7 +7797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:8" ht="15.6">
       <c r="A270" s="33" t="s">
         <v>23</v>
       </c>
@@ -7807,7 +7823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" ht="31.2">
       <c r="A271" s="33" t="s">
         <v>17</v>
       </c>
@@ -7833,7 +7849,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" ht="15.6">
       <c r="A272" s="33" t="s">
         <v>21</v>
       </c>
@@ -7859,7 +7875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" ht="15.6">
       <c r="A273" s="33" t="s">
         <v>12</v>
       </c>
@@ -7885,7 +7901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:8" ht="15.6">
       <c r="A274" s="33" t="s">
         <v>20</v>
       </c>
@@ -7911,7 +7927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" ht="15.6">
       <c r="A275" s="33" t="s">
         <v>18</v>
       </c>
@@ -7937,7 +7953,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:8" ht="15.6">
       <c r="A276" s="55" t="s">
         <v>27</v>
       </c>
@@ -7963,7 +7979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" ht="15.6">
       <c r="A277" s="33" t="s">
         <v>28</v>
       </c>
@@ -7989,57 +8005,57 @@
         <v>34</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A279" s="65" t="s">
+    <row r="279" spans="1:8" ht="15.6">
+      <c r="A279" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B279" s="66">
+      <c r="B279" s="58">
         <v>46272</v>
       </c>
-      <c r="C279" s="66">
+      <c r="C279" s="58">
         <v>46273</v>
       </c>
-      <c r="D279" s="66">
+      <c r="D279" s="58">
         <v>46274</v>
       </c>
-      <c r="E279" s="66">
+      <c r="E279" s="58">
         <v>46275</v>
       </c>
-      <c r="F279" s="66">
+      <c r="F279" s="58">
         <v>46276</v>
       </c>
-      <c r="G279" s="66">
+      <c r="G279" s="58">
         <v>46277</v>
       </c>
-      <c r="H279" s="66">
+      <c r="H279" s="58">
         <v>46278</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A280" s="65"/>
-      <c r="B280" s="67" t="s">
+    <row r="280" spans="1:8" ht="15.6">
+      <c r="A280" s="60"/>
+      <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C280" s="67" t="s">
+      <c r="C280" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="D280" s="67" t="s">
+      <c r="D280" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="E280" s="67" t="s">
+      <c r="E280" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="F280" s="67" t="s">
+      <c r="F280" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="G280" s="67" t="s">
+      <c r="G280" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="H280" s="67" t="s">
+      <c r="H280" s="59" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:8" ht="15.6">
       <c r="A281" s="33" t="s">
         <v>22</v>
       </c>
@@ -8065,7 +8081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:8" ht="15.6">
       <c r="A282" s="33" t="s">
         <v>20</v>
       </c>
@@ -8091,7 +8107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:8" ht="31.2">
       <c r="A283" s="33" t="s">
         <v>17</v>
       </c>
@@ -8117,7 +8133,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:8" ht="15.6">
       <c r="A284" s="33" t="s">
         <v>23</v>
       </c>
@@ -8143,7 +8159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:8" ht="15.6">
       <c r="A285" s="33" t="s">
         <v>21</v>
       </c>
@@ -8169,7 +8185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:8" ht="15.6">
       <c r="A286" s="33" t="s">
         <v>8</v>
       </c>
@@ -8195,7 +8211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:8" ht="15.6">
       <c r="A287" s="33" t="s">
         <v>14</v>
       </c>
@@ -8221,7 +8237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:8" ht="15.6">
       <c r="A288" s="33" t="s">
         <v>12</v>
       </c>
@@ -8247,7 +8263,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:8" ht="15.6">
       <c r="A289" s="33" t="s">
         <v>18</v>
       </c>
@@ -8273,7 +8289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:8" ht="15.6">
       <c r="A290" s="55" t="s">
         <v>27</v>
       </c>
@@ -8299,7 +8315,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:8" ht="15.6">
       <c r="A291" s="33" t="s">
         <v>28</v>
       </c>
@@ -8325,8 +8341,355 @@
         <v>10</v>
       </c>
     </row>
+    <row r="293" spans="1:8" ht="15.6">
+      <c r="A293" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B293" s="47">
+        <v>46279</v>
+      </c>
+      <c r="C293" s="47">
+        <v>46280</v>
+      </c>
+      <c r="D293" s="47">
+        <v>46281</v>
+      </c>
+      <c r="E293" s="47">
+        <v>46282</v>
+      </c>
+      <c r="F293" s="47">
+        <v>46283</v>
+      </c>
+      <c r="G293" s="47">
+        <v>46284</v>
+      </c>
+      <c r="H293" s="47">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="15.6">
+      <c r="A294" s="62"/>
+      <c r="B294" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C294" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D294" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E294" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F294" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G294" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H294" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" ht="15.6">
+      <c r="A295" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B295" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C295" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D295" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E295" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F295" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G295" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H295" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" ht="31.2">
+      <c r="A296" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B296" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C296" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="D296" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="E296" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="F296" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G296" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="H296" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" ht="31.2">
+      <c r="A297" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B297" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="C297" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="D297" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="E297" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="F297" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G297" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="H297" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" ht="15.6">
+      <c r="A298" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B298" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C298" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D298" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E298" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F298" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G298" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H298" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" ht="15.6">
+      <c r="A299" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B299" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C299" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D299" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E299" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F299" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G299" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H299" s="68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" ht="15.6">
+      <c r="A300" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B300" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D300" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E300" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="F300" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G300" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H300" s="68" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" ht="15.6">
+      <c r="A301" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B301" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C301" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D301" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E301" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="F301" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G301" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H301" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" ht="15.6">
+      <c r="A302" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B302" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C302" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D302" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E302" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="F302" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G302" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H302" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" ht="15.6">
+      <c r="A303" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B303" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C303" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D303" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E303" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F303" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G303" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H303" s="68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" ht="15.6">
+      <c r="A304" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B304" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C304" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D304" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E304" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="F304" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G304" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H304" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" ht="15.6">
+      <c r="A305" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B305" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C305" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="D305" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="E305" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="F305" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G305" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="H305" s="70" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A293:A294"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="A265:A266"/>
     <mergeCell ref="G84:H84"/>
@@ -8338,16 +8701,6 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8356,17 +8709,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -8567,6 +8909,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8577,17 +8930,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8606,6 +8948,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>

--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA6AF27-50E5-48ED-A5E8-99D3689D5F08}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB492C66-638D-467D-9859-4EFA5EDE96BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -643,20 +643,20 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -667,14 +667,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3338,8 +3338,8 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="63"/>
-      <c r="H84" s="64"/>
+      <c r="G84" s="69"/>
+      <c r="H84" s="70"/>
     </row>
     <row r="85" spans="1:8" ht="15.6">
       <c r="A85" s="3" t="s">
@@ -6212,7 +6212,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.6">
-      <c r="A205" s="61" t="s">
+      <c r="A205" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="26">
@@ -6238,7 +6238,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.6">
-      <c r="A206" s="61"/>
+      <c r="A206" s="63"/>
       <c r="B206" s="23" t="s">
         <v>1</v>
       </c>
@@ -6584,7 +6584,7 @@
       <c r="H219" s="22"/>
     </row>
     <row r="220" spans="1:8" ht="15.6">
-      <c r="A220" s="61" t="s">
+      <c r="A220" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="26">
@@ -6610,7 +6610,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="15.6">
-      <c r="A221" s="61"/>
+      <c r="A221" s="63"/>
       <c r="B221" s="23" t="s">
         <v>1</v>
       </c>
@@ -6946,7 +6946,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="15.6">
-      <c r="A235" s="61" t="s">
+      <c r="A235" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B235" s="26">
@@ -6972,7 +6972,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="15.6">
-      <c r="A236" s="61"/>
+      <c r="A236" s="63"/>
       <c r="B236" s="23" t="s">
         <v>1</v>
       </c>
@@ -7308,7 +7308,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="15.6">
-      <c r="A250" s="61" t="s">
+      <c r="A250" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B250" s="47">
@@ -7334,7 +7334,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="15.6">
-      <c r="A251" s="61"/>
+      <c r="A251" s="63"/>
       <c r="B251" s="48" t="s">
         <v>1</v>
       </c>
@@ -7670,7 +7670,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="15.6">
-      <c r="A265" s="61" t="s">
+      <c r="A265" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B265" s="11" t="s">
@@ -7696,7 +7696,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="15.6">
-      <c r="A266" s="62"/>
+      <c r="A266" s="64"/>
       <c r="B266" s="48" t="s">
         <v>1</v>
       </c>
@@ -8006,7 +8006,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="15.6">
-      <c r="A279" s="60" t="s">
+      <c r="A279" s="68" t="s">
         <v>0</v>
       </c>
       <c r="B279" s="58">
@@ -8032,7 +8032,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="15.6">
-      <c r="A280" s="60"/>
+      <c r="A280" s="68"/>
       <c r="B280" s="59" t="s">
         <v>1</v>
       </c>
@@ -8342,7 +8342,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.6">
-      <c r="A293" s="61" t="s">
+      <c r="A293" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B293" s="47">
@@ -8368,7 +8368,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.6">
-      <c r="A294" s="62"/>
+      <c r="A294" s="64"/>
       <c r="B294" s="48" t="s">
         <v>1</v>
       </c>
@@ -8395,22 +8395,22 @@
       <c r="A295" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B295" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C295" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="D295" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E295" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F295" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="G295" s="68" t="s">
+      <c r="B295" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C295" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D295" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E295" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F295" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G295" s="60" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="29" t="s">
@@ -8421,22 +8421,22 @@
       <c r="A296" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B296" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C296" s="68" t="s">
+      <c r="B296" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C296" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="D296" s="68" t="s">
+      <c r="D296" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="E296" s="68" t="s">
+      <c r="E296" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="F296" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="G296" s="68" t="s">
+      <c r="F296" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G296" s="60" t="s">
         <v>11</v>
       </c>
       <c r="H296" s="29" t="s">
@@ -8447,22 +8447,22 @@
       <c r="A297" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B297" s="68" t="s">
+      <c r="B297" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="C297" s="68" t="s">
+      <c r="C297" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D297" s="68" t="s">
+      <c r="D297" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="E297" s="68" t="s">
+      <c r="E297" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="F297" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="G297" s="68" t="s">
+      <c r="F297" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G297" s="60" t="s">
         <v>11</v>
       </c>
       <c r="H297" s="29" t="s">
@@ -8473,25 +8473,25 @@
       <c r="A298" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B298" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C298" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="D298" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E298" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F298" s="68" t="s">
+      <c r="B298" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C298" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D298" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E298" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F298" s="60" t="s">
         <v>9</v>
       </c>
       <c r="G298" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H298" s="68" t="s">
+      <c r="H298" s="60" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8499,25 +8499,25 @@
       <c r="A299" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B299" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C299" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="D299" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E299" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F299" s="68" t="s">
+      <c r="B299" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C299" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D299" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E299" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F299" s="60" t="s">
         <v>9</v>
       </c>
       <c r="G299" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H299" s="68" t="s">
+      <c r="H299" s="60" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8525,25 +8525,25 @@
       <c r="A300" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B300" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="C300" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="D300" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E300" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F300" s="68" t="s">
+      <c r="B300" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D300" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E300" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="F300" s="60" t="s">
         <v>11</v>
       </c>
       <c r="G300" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H300" s="68" t="s">
+      <c r="H300" s="60" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8551,22 +8551,22 @@
       <c r="A301" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B301" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="C301" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="D301" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E301" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F301" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="G301" s="68" t="s">
+      <c r="B301" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C301" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D301" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E301" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="F301" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G301" s="60" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="29" t="s">
@@ -8577,22 +8577,22 @@
       <c r="A302" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B302" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="C302" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="D302" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="E302" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="F302" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="G302" s="68" t="s">
+      <c r="B302" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C302" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D302" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E302" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F302" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G302" s="60" t="s">
         <v>13</v>
       </c>
       <c r="H302" s="29" t="s">
@@ -8603,25 +8603,25 @@
       <c r="A303" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B303" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C303" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="D303" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E303" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F303" s="68" t="s">
+      <c r="B303" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C303" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D303" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E303" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F303" s="60" t="s">
         <v>9</v>
       </c>
       <c r="G303" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H303" s="68" t="s">
+      <c r="H303" s="60" t="s">
         <v>26</v>
       </c>
     </row>
@@ -8629,20 +8629,20 @@
       <c r="A304" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B304" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="C304" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="D304" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E304" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F304" s="68" t="s">
-        <v>11</v>
+      <c r="B304" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="C304" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D304" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E304" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F304" s="60" t="s">
+        <v>33</v>
       </c>
       <c r="G304" s="29" t="s">
         <v>10</v>
@@ -8655,43 +8655,30 @@
       <c r="A305" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B305" s="68" t="s">
+      <c r="B305" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="C305" s="68" t="s">
+      <c r="C305" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="D305" s="68" t="s">
+      <c r="D305" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="E305" s="68" t="s">
+      <c r="E305" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="F305" s="68" t="s">
+      <c r="F305" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="G305" s="69" t="s">
+      <c r="G305" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="H305" s="70" t="s">
+      <c r="H305" s="62" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A293:A294"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A279:A280"/>
-    <mergeCell ref="A265:A266"/>
     <mergeCell ref="G84:H84"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="A160:A161"/>
@@ -8701,6 +8688,19 @@
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A293:A294"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A279:A280"/>
+    <mergeCell ref="A265:A266"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8709,6 +8709,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -8909,27 +8929,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8946,23 +8965,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>